--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07490000000000001</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="E2">
-        <v>0.07113999999999999</v>
+        <v>0.01825</v>
       </c>
       <c r="F2">
-        <v>0.019335</v>
+        <v>0.0941</v>
       </c>
       <c r="G2">
-        <v>0.5175063872346229</v>
+        <v>0.139253761267425</v>
       </c>
       <c r="H2">
-        <v>0.51703414101923</v>
+        <v>0.1388888335968176</v>
       </c>
       <c r="I2">
-        <v>0.5673676969363806</v>
+        <v>0.1679386801974517</v>
       </c>
       <c r="J2">
-        <v>0.5080903167429582</v>
+        <v>0.1528002431028151</v>
       </c>
       <c r="K2">
-        <v>6991.7</v>
+        <v>9361.722</v>
       </c>
       <c r="L2">
-        <v>0.6356957766968223</v>
+        <v>0.151501170835233</v>
       </c>
       <c r="M2">
-        <v>2257.9</v>
+        <v>5352.6288</v>
       </c>
       <c r="N2">
-        <v>0.03737366380751545</v>
+        <v>0.0476146865868141</v>
       </c>
       <c r="O2">
-        <v>0.3229400574967461</v>
+        <v>0.5717568626797507</v>
       </c>
       <c r="P2">
-        <v>1681.5</v>
+        <v>4028.7818</v>
       </c>
       <c r="Q2">
-        <v>0.02783286048644193</v>
+        <v>0.03583831233237409</v>
       </c>
       <c r="R2">
-        <v>0.240499449347083</v>
+        <v>0.4303462333104957</v>
       </c>
       <c r="S2">
-        <v>576.4000000000001</v>
+        <v>1323.847</v>
       </c>
       <c r="T2">
-        <v>0.2552814562203818</v>
+        <v>0.2473265099197613</v>
       </c>
       <c r="U2">
-        <v>4811</v>
+        <v>11132.246</v>
       </c>
       <c r="V2">
-        <v>0.07963359607509492</v>
+        <v>0.09902767856745733</v>
       </c>
       <c r="W2">
-        <v>0.1501569783010504</v>
+        <v>0.02987624880961848</v>
       </c>
       <c r="X2">
-        <v>0.07550689090187979</v>
+        <v>0.07215710645368037</v>
       </c>
       <c r="Y2">
-        <v>0.07465008739917062</v>
+        <v>-0.04228085764406189</v>
       </c>
       <c r="Z2">
-        <v>0.3192604276708903</v>
+        <v>0.8806581654044771</v>
       </c>
       <c r="AA2">
-        <v>0.1055582311717276</v>
+        <v>0.03663057171674357</v>
       </c>
       <c r="AB2">
-        <v>0.07120268352746932</v>
+        <v>0.07197194610460914</v>
       </c>
       <c r="AC2">
-        <v>0.03436134291791953</v>
+        <v>-0.03536532960397276</v>
       </c>
       <c r="AD2">
-        <v>4915.6</v>
+        <v>8800.353999999999</v>
       </c>
       <c r="AE2">
-        <v>70.0319262260921</v>
+        <v>70.63941333645529</v>
       </c>
       <c r="AF2">
-        <v>4985.631926226092</v>
+        <v>8870.993413336455</v>
       </c>
       <c r="AG2">
-        <v>174.6319262260922</v>
+        <v>-2261.252586663544</v>
       </c>
       <c r="AH2">
-        <v>0.07623309998487619</v>
+        <v>0.07314081859968272</v>
       </c>
       <c r="AI2">
-        <v>0.1017290467323598</v>
+        <v>0.09325982606213407</v>
       </c>
       <c r="AJ2">
-        <v>0.002882246128110322</v>
+        <v>-0.02052805624624305</v>
       </c>
       <c r="AK2">
-        <v>0.003951133426730979</v>
+        <v>-0.02692319052029508</v>
       </c>
       <c r="AL2">
-        <v>135.4</v>
+        <v>497.947</v>
       </c>
       <c r="AM2">
-        <v>-64.19999999999999</v>
+        <v>27.94600000000003</v>
       </c>
       <c r="AN2">
-        <v>0.7637188490460507</v>
+        <v>0.8777973678309782</v>
       </c>
       <c r="AO2">
-        <v>46.01255539143278</v>
+        <v>20.8191454110578</v>
       </c>
       <c r="AP2">
-        <v>0.02713192564571689</v>
+        <v>-0.2255501958869212</v>
       </c>
       <c r="AQ2">
-        <v>-97.04205607476636</v>
+        <v>370.9593859586342</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3i Group plc (LSE:III)</t>
+          <t>Quilter plc (LSE:QLT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.253</v>
+        <v>0.163</v>
       </c>
       <c r="E3">
-        <v>0.268</v>
+        <v>-0.173</v>
       </c>
       <c r="F3">
-        <v>0.131</v>
+        <v>0.101</v>
       </c>
       <c r="G3">
-        <v>0.8394333350737048</v>
+        <v>0.02883635647658192</v>
       </c>
       <c r="H3">
-        <v>0.8394333350737048</v>
+        <v>0.0285250178435185</v>
       </c>
       <c r="I3">
-        <v>0.9608068361788406</v>
+        <v>0.02846348846939529</v>
       </c>
       <c r="J3">
-        <v>0.9603509292523251</v>
+        <v>0.01423174423469765</v>
       </c>
       <c r="K3">
-        <v>5645.4</v>
+        <v>63.2</v>
       </c>
       <c r="L3">
-        <v>0.9825092674776797</v>
+        <v>0.007777312889173292</v>
       </c>
       <c r="M3">
-        <v>786.8</v>
+        <v>113.8</v>
       </c>
       <c r="N3">
-        <v>0.01828500248664879</v>
+        <v>0.04366343091739247</v>
       </c>
       <c r="O3">
-        <v>0.1393701066354908</v>
+        <v>1.800632911392405</v>
       </c>
       <c r="P3">
-        <v>786.8</v>
+        <v>88.5</v>
       </c>
       <c r="Q3">
-        <v>0.01828500248664879</v>
+        <v>0.03395618309480873</v>
       </c>
       <c r="R3">
-        <v>0.1393701066354908</v>
+        <v>1.400316455696202</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.2223198594024604</v>
       </c>
       <c r="U3">
-        <v>494.6</v>
+        <v>1934.9</v>
       </c>
       <c r="V3">
-        <v>0.01149435972279676</v>
+        <v>0.7423934313010782</v>
       </c>
       <c r="W3">
-        <v>0.2535583232650788</v>
+        <v>0.03304575163398693</v>
       </c>
       <c r="X3">
-        <v>0.07278902215087199</v>
+        <v>0.07466017351365382</v>
       </c>
       <c r="Y3">
-        <v>0.1807693011142068</v>
+        <v>-0.04161442187966689</v>
       </c>
       <c r="Z3">
-        <v>0.242294798540977</v>
+        <v>1625.239999999963</v>
       </c>
       <c r="AA3">
-        <v>0.2326880349318322</v>
+        <v>5</v>
       </c>
       <c r="AB3">
-        <v>0.07179240862533963</v>
+        <v>0.07125761563009093</v>
       </c>
       <c r="AC3">
-        <v>0.1608956263064926</v>
+        <v>4.928742384369909</v>
       </c>
       <c r="AD3">
-        <v>1658</v>
+        <v>350.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1658</v>
+        <v>350.1</v>
       </c>
       <c r="AG3">
-        <v>1163.4</v>
+        <v>-1584.8</v>
       </c>
       <c r="AH3">
-        <v>0.03710184882674913</v>
+        <v>0.118421052631579</v>
       </c>
       <c r="AI3">
-        <v>0.05347938559991743</v>
+        <v>0.1574898785425101</v>
       </c>
       <c r="AJ3">
-        <v>0.02632531701709765</v>
+        <v>-1.551443954968184</v>
       </c>
       <c r="AK3">
-        <v>0.03813425986626459</v>
+        <v>-5.500867754251998</v>
       </c>
       <c r="AL3">
-        <v>89.8</v>
+        <v>26.5</v>
       </c>
       <c r="AM3">
-        <v>72.40000000000001</v>
+        <v>26.5</v>
       </c>
       <c r="AN3">
-        <v>0.3000687733014805</v>
+        <v>1.231012658227848</v>
       </c>
       <c r="AO3">
-        <v>61.47772828507795</v>
+        <v>8.728301886792453</v>
       </c>
       <c r="AP3">
-        <v>0.2105548919535238</v>
+        <v>-5.572433192686359</v>
       </c>
       <c r="AQ3">
-        <v>76.25276243093921</v>
+        <v>8.728301886792453</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Janus Henderson Group plc (NYSE:JHG)</t>
+          <t>Foresight Group Holdings Limited (LSE:FSG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,125 +861,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0178</v>
-      </c>
-      <c r="E4">
-        <v>-0.00672</v>
-      </c>
       <c r="F4">
-        <v>0.0476</v>
+        <v>0.158</v>
       </c>
       <c r="G4">
-        <v>0.2171080826262107</v>
+        <v>0.257884028484232</v>
       </c>
       <c r="H4">
-        <v>0.2171080826262107</v>
+        <v>0.257884028484232</v>
       </c>
       <c r="I4">
-        <v>0.2579898923265542</v>
+        <v>0.3255340793489319</v>
       </c>
       <c r="J4">
-        <v>0.1951905436371474</v>
+        <v>0.2707281390122963</v>
       </c>
       <c r="K4">
-        <v>408.4</v>
+        <v>41</v>
       </c>
       <c r="L4">
-        <v>0.1750235707551213</v>
+        <v>0.2085452695829095</v>
       </c>
       <c r="M4">
-        <v>549.9000000000001</v>
+        <v>42.4</v>
       </c>
       <c r="N4">
-        <v>0.0819034852546917</v>
+        <v>0.0719253604749788</v>
       </c>
       <c r="O4">
-        <v>1.346474045053869</v>
+        <v>1.034146341463415</v>
       </c>
       <c r="P4">
-        <v>252.8</v>
+        <v>34.6</v>
       </c>
       <c r="Q4">
-        <v>0.03765266607089664</v>
+        <v>0.05869380831212893</v>
       </c>
       <c r="R4">
-        <v>0.6190009794319296</v>
+        <v>0.8439024390243903</v>
       </c>
       <c r="S4">
-        <v>297.1000000000001</v>
+        <v>7.799999999999997</v>
       </c>
       <c r="T4">
-        <v>0.5402800509183489</v>
+        <v>0.1839622641509433</v>
       </c>
       <c r="U4">
-        <v>1504.8</v>
+        <v>70.2</v>
       </c>
       <c r="V4">
-        <v>0.2241286863270777</v>
+        <v>0.1190839694656489</v>
       </c>
       <c r="W4">
-        <v>0.09165376242734352</v>
+        <v>0.4456521739130435</v>
       </c>
       <c r="X4">
-        <v>0.07428321501771522</v>
+        <v>0.07288935598394555</v>
       </c>
       <c r="Y4">
-        <v>0.0173705474096283</v>
+        <v>0.3727628179290979</v>
       </c>
       <c r="Z4">
-        <v>0.9597998260926122</v>
+        <v>9.018348623853212</v>
       </c>
       <c r="AA4">
-        <v>0.1873438498378565</v>
+        <v>2.441520739899883</v>
       </c>
       <c r="AB4">
-        <v>0.07145519734303049</v>
+        <v>0.07174623476885154</v>
       </c>
       <c r="AC4">
-        <v>0.115888652494826</v>
+        <v>2.369774505131032</v>
       </c>
       <c r="AD4">
-        <v>698.6</v>
+        <v>26.1</v>
       </c>
       <c r="AE4">
-        <v>70.0319262260921</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>768.6319262260921</v>
+        <v>26.1</v>
       </c>
       <c r="AG4">
-        <v>-736.1680737739078</v>
+        <v>-44.1</v>
       </c>
       <c r="AH4">
-        <v>0.102722134912462</v>
+        <v>0.04239766081871345</v>
       </c>
       <c r="AI4">
-        <v>0.1303797539892098</v>
+        <v>0.192619926199262</v>
       </c>
       <c r="AJ4">
-        <v>-0.1231496774849378</v>
+        <v>-0.08085808580858087</v>
       </c>
       <c r="AK4">
-        <v>-0.1676717277413549</v>
+        <v>-0.675344563552833</v>
       </c>
       <c r="AL4">
-        <v>14</v>
+        <v>1.06</v>
       </c>
       <c r="AM4">
-        <v>-74.7</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="AN4">
-        <v>1.097047738693467</v>
+        <v>0.3739255014326648</v>
       </c>
       <c r="AO4">
-        <v>42.27857142857142</v>
+        <v>60.37735849056603</v>
       </c>
       <c r="AP4">
-        <v>-1.156042829418825</v>
+        <v>-0.6318051575931233</v>
       </c>
       <c r="AQ4">
-        <v>-7.923694779116465</v>
+        <v>-145.4545454545455</v>
       </c>
     </row>
     <row r="5">
@@ -990,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>abrdn plc (LSE:ABDN)</t>
+          <t>Tatton Asset Management plc (AIM:TAM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -999,124 +993,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.124</v>
+        <v>0.16</v>
       </c>
       <c r="E5">
-        <v>-0.247</v>
+        <v>0.233</v>
       </c>
       <c r="F5">
-        <v>-0.0209</v>
+        <v>0.15</v>
       </c>
       <c r="G5">
-        <v>0.2033044846577498</v>
+        <v>0.3459357277882798</v>
       </c>
       <c r="H5">
-        <v>0.2004608294930876</v>
+        <v>0.3459357277882798</v>
       </c>
       <c r="I5">
-        <v>0.06603349443632685</v>
+        <v>0.4007561436672968</v>
       </c>
       <c r="J5">
-        <v>0.06188307357869654</v>
+        <v>0.3190455525071164</v>
       </c>
       <c r="K5">
-        <v>400.6</v>
+        <v>20.6</v>
       </c>
       <c r="L5">
-        <v>0.2251320669888726</v>
+        <v>0.389413988657845</v>
       </c>
       <c r="M5">
-        <v>616.7</v>
+        <v>13.753</v>
       </c>
       <c r="N5">
-        <v>0.1955728918910348</v>
+        <v>0.02688232994526974</v>
       </c>
       <c r="O5">
-        <v>1.539440838741887</v>
+        <v>0.6676213592233009</v>
       </c>
       <c r="P5">
-        <v>337.4</v>
+        <v>12.8</v>
       </c>
       <c r="Q5">
-        <v>0.1069990169029271</v>
+        <v>0.02501954652071931</v>
       </c>
       <c r="R5">
-        <v>0.8422366450324512</v>
+        <v>0.6213592233009708</v>
       </c>
       <c r="S5">
-        <v>279.3000000000001</v>
+        <v>0.9529999999999994</v>
       </c>
       <c r="T5">
-        <v>0.4528944381384791</v>
+        <v>0.06929397222424194</v>
       </c>
       <c r="U5">
-        <v>1765.5</v>
+        <v>36.1</v>
       </c>
       <c r="V5">
-        <v>0.5598896394253638</v>
+        <v>0.07056293979671618</v>
       </c>
       <c r="W5">
-        <v>0.0587907249779865</v>
+        <v>0.4186991869918699</v>
       </c>
       <c r="X5">
-        <v>0.07679316415568821</v>
+        <v>0.0720480608595131</v>
       </c>
       <c r="Y5">
-        <v>-0.01800243917770171</v>
+        <v>0.3466511261323568</v>
       </c>
       <c r="Z5">
-        <v>0.3841537132987911</v>
+        <v>6.388117377128363</v>
       </c>
       <c r="AA5">
-        <v>0.02377261250559858</v>
+        <v>2.03810043806623</v>
       </c>
       <c r="AB5">
-        <v>0.07093857916458557</v>
+        <v>0.07200525353043065</v>
       </c>
       <c r="AC5">
-        <v>-0.04716596665898699</v>
+        <v>1.966095184535799</v>
       </c>
       <c r="AD5">
-        <v>763.3</v>
+        <v>0.763</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>763.3</v>
+        <v>0.763</v>
       </c>
       <c r="AG5">
-        <v>-1002.2</v>
+        <v>-35.337</v>
       </c>
       <c r="AH5">
-        <v>0.1948884236327427</v>
+        <v>0.001489178570661816</v>
       </c>
       <c r="AI5">
-        <v>0.1050943136444995</v>
+        <v>0.01187308404525154</v>
       </c>
       <c r="AJ5">
-        <v>-0.46590116684487</v>
+        <v>-0.07419639988829702</v>
       </c>
       <c r="AK5">
-        <v>-0.1823010459299682</v>
+        <v>-1.25473138515073</v>
       </c>
       <c r="AL5">
-        <v>31.6</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>-61.9</v>
+        <v>-1.33</v>
       </c>
       <c r="AN5">
-        <v>2.783734500364697</v>
-      </c>
-      <c r="AO5">
-        <v>3.718354430379747</v>
+        <v>0.03484018264840183</v>
       </c>
       <c r="AP5">
-        <v>-3.654996353026988</v>
+        <v>-1.613561643835617</v>
       </c>
       <c r="AQ5">
-        <v>-1.898222940226171</v>
+        <v>-15.93984962406015</v>
       </c>
     </row>
     <row r="6">
@@ -1127,121 +1118,9161 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Jupiter Fund Management Plc (LSE:JUP)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.0144</v>
+      </c>
+      <c r="F6">
+        <v>-0.16</v>
+      </c>
+      <c r="G6">
+        <v>0.3024731888815934</v>
+      </c>
+      <c r="H6">
+        <v>0.3024731888815934</v>
+      </c>
+      <c r="I6">
+        <v>0.2409717662508208</v>
+      </c>
+      <c r="J6">
+        <v>0.1204858831254104</v>
+      </c>
+      <c r="K6">
+        <v>-11.2</v>
+      </c>
+      <c r="L6">
+        <v>-0.02451302254322609</v>
+      </c>
+      <c r="M6">
+        <v>45.96</v>
+      </c>
+      <c r="N6">
+        <v>0.08275117032769176</v>
+      </c>
+      <c r="O6">
+        <v>-4.103571428571429</v>
+      </c>
+      <c r="P6">
+        <v>44.7</v>
+      </c>
+      <c r="Q6">
+        <v>0.08048253510983076</v>
+      </c>
+      <c r="R6">
+        <v>-3.991071428571429</v>
+      </c>
+      <c r="S6">
+        <v>1.259999999999998</v>
+      </c>
+      <c r="T6">
+        <v>0.02741514360313312</v>
+      </c>
+      <c r="U6">
+        <v>261.5</v>
+      </c>
+      <c r="V6">
+        <v>0.4708318329132157</v>
+      </c>
+      <c r="W6">
+        <v>-0.01038479369494669</v>
+      </c>
+      <c r="X6">
+        <v>0.07606908926755428</v>
+      </c>
+      <c r="Y6">
+        <v>-0.08645388296250096</v>
+      </c>
+      <c r="Z6">
+        <v>8.232432432432432</v>
+      </c>
+      <c r="AA6">
+        <v>0.9918918918918919</v>
+      </c>
+      <c r="AB6">
+        <v>0.07092098221684842</v>
+      </c>
+      <c r="AC6">
+        <v>0.9209709096750435</v>
+      </c>
+      <c r="AD6">
+        <v>114.4</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>114.4</v>
+      </c>
+      <c r="AG6">
+        <v>-147.1</v>
+      </c>
+      <c r="AH6">
+        <v>0.1707972529113168</v>
+      </c>
+      <c r="AI6">
+        <v>0.1010154525386314</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.3602743081067842</v>
+      </c>
+      <c r="AK6">
+        <v>-0.168886337543054</v>
+      </c>
+      <c r="AL6">
+        <v>7.58</v>
+      </c>
+      <c r="AM6">
+        <v>-4.32</v>
+      </c>
+      <c r="AN6">
+        <v>0.8411764705882353</v>
+      </c>
+      <c r="AO6">
+        <v>14.52506596306069</v>
+      </c>
+      <c r="AP6">
+        <v>-1.081617647058823</v>
+      </c>
+      <c r="AQ6">
+        <v>-25.48611111111111</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Polar Capital Holdings Plc (AIM:POLR)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0385</v>
+      </c>
+      <c r="E7">
+        <v>-0.0364</v>
+      </c>
+      <c r="F7">
+        <v>0.0941</v>
+      </c>
+      <c r="G7">
+        <v>0.2490354261662574</v>
+      </c>
+      <c r="H7">
+        <v>0.2490354261662574</v>
+      </c>
+      <c r="I7">
+        <v>0.2851631006664328</v>
+      </c>
+      <c r="J7">
+        <v>0.2102187903730208</v>
+      </c>
+      <c r="K7">
+        <v>56</v>
+      </c>
+      <c r="L7">
+        <v>0.1964223079621185</v>
+      </c>
+      <c r="M7">
+        <v>65.63</v>
+      </c>
+      <c r="N7">
+        <v>0.1070461588647855</v>
+      </c>
+      <c r="O7">
+        <v>1.171964285714286</v>
+      </c>
+      <c r="P7">
+        <v>59.4</v>
+      </c>
+      <c r="Q7">
+        <v>0.09688468439080085</v>
+      </c>
+      <c r="R7">
+        <v>1.060714285714286</v>
+      </c>
+      <c r="S7">
+        <v>6.229999999999997</v>
+      </c>
+      <c r="T7">
+        <v>0.09492610086850521</v>
+      </c>
+      <c r="U7">
+        <v>91.5</v>
+      </c>
+      <c r="V7">
+        <v>0.1492415592888599</v>
+      </c>
+      <c r="W7">
+        <v>0.3728362183754994</v>
+      </c>
+      <c r="X7">
+        <v>0.07229039351431077</v>
+      </c>
+      <c r="Y7">
+        <v>0.3005458248611886</v>
+      </c>
+      <c r="Z7">
+        <v>4.477072864321609</v>
+      </c>
+      <c r="AA7">
+        <v>0.9411648419495641</v>
+      </c>
+      <c r="AB7">
+        <v>0.0719311515532807</v>
+      </c>
+      <c r="AC7">
+        <v>0.8692336903962834</v>
+      </c>
+      <c r="AD7">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="AG7">
+        <v>-83.03</v>
+      </c>
+      <c r="AH7">
+        <v>0.01362678378943643</v>
+      </c>
+      <c r="AI7">
+        <v>0.04829788447282888</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.1566396890976663</v>
+      </c>
+      <c r="AK7">
+        <v>-0.9899844998211518</v>
+      </c>
+      <c r="AL7">
+        <v>0.272</v>
+      </c>
+      <c r="AM7">
+        <v>0.272</v>
+      </c>
+      <c r="AN7">
+        <v>0.1015587529976019</v>
+      </c>
+      <c r="AO7">
+        <v>298.8970588235294</v>
+      </c>
+      <c r="AP7">
+        <v>-0.9955635491606714</v>
+      </c>
+      <c r="AQ7">
+        <v>298.8970588235294</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hargreaves Lansdown plc (LSE:HL.)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0974</v>
+      </c>
+      <c r="E8">
+        <v>0.0346</v>
+      </c>
+      <c r="F8">
+        <v>0.102</v>
+      </c>
+      <c r="G8">
+        <v>0.5118547636288404</v>
+      </c>
+      <c r="H8">
+        <v>0.5058446260473777</v>
+      </c>
+      <c r="I8">
+        <v>0.498189717595945</v>
+      </c>
+      <c r="J8">
+        <v>0.368568870545722</v>
+      </c>
+      <c r="K8">
+        <v>370.5</v>
+      </c>
+      <c r="L8">
+        <v>0.3832626461156511</v>
+      </c>
+      <c r="M8">
+        <v>251.7</v>
+      </c>
+      <c r="N8">
+        <v>0.03861613992022093</v>
+      </c>
+      <c r="O8">
+        <v>0.6793522267206478</v>
+      </c>
+      <c r="P8">
+        <v>251.7</v>
+      </c>
+      <c r="Q8">
+        <v>0.03861613992022093</v>
+      </c>
+      <c r="R8">
+        <v>0.6793522267206478</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>778.9</v>
+      </c>
+      <c r="V8">
+        <v>0.1194998465787051</v>
+      </c>
+      <c r="W8">
+        <v>0.4107994234394057</v>
+      </c>
+      <c r="X8">
+        <v>0.07205161794039239</v>
+      </c>
+      <c r="Y8">
+        <v>0.3387478054990133</v>
+      </c>
+      <c r="Z8">
+        <v>2.1575716995871</v>
+      </c>
+      <c r="AA8">
+        <v>0.7952137644382312</v>
+      </c>
+      <c r="AB8">
+        <v>0.07200800365707759</v>
+      </c>
+      <c r="AC8">
+        <v>0.7232057607811536</v>
+      </c>
+      <c r="AD8">
+        <v>10.9</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>10.9</v>
+      </c>
+      <c r="AG8">
+        <v>-768</v>
+      </c>
+      <c r="AH8">
+        <v>0.001669500222089479</v>
+      </c>
+      <c r="AI8">
+        <v>0.01047070124879923</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.1335652173913043</v>
+      </c>
+      <c r="AK8">
+        <v>-2.930179320869898</v>
+      </c>
+      <c r="AL8">
+        <v>0.379</v>
+      </c>
+      <c r="AM8">
+        <v>-37.421</v>
+      </c>
+      <c r="AN8">
+        <v>0.02229038854805726</v>
+      </c>
+      <c r="AO8">
+        <v>1270.712401055409</v>
+      </c>
+      <c r="AP8">
+        <v>-1.570552147239264</v>
+      </c>
+      <c r="AQ8">
+        <v>-12.86977900109564</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Record plc (LSE:REC)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.137</v>
+      </c>
+      <c r="E9">
+        <v>0.106</v>
+      </c>
+      <c r="G9">
+        <v>0.3117744610281924</v>
+      </c>
+      <c r="H9">
+        <v>0.3117744610281924</v>
+      </c>
+      <c r="I9">
+        <v>0.3134328358208955</v>
+      </c>
+      <c r="J9">
+        <v>0.2194029850746269</v>
+      </c>
+      <c r="K9">
+        <v>12.7</v>
+      </c>
+      <c r="L9">
+        <v>0.2106135986733002</v>
+      </c>
+      <c r="M9">
+        <v>8.786</v>
+      </c>
+      <c r="N9">
+        <v>0.06858704137392661</v>
+      </c>
+      <c r="O9">
+        <v>0.6918110236220473</v>
+      </c>
+      <c r="P9">
+        <v>8.35</v>
+      </c>
+      <c r="Q9">
+        <v>0.06518345042935207</v>
+      </c>
+      <c r="R9">
+        <v>0.65748031496063</v>
+      </c>
+      <c r="S9">
+        <v>0.4359999999999999</v>
+      </c>
+      <c r="T9">
+        <v>0.04962440245845663</v>
+      </c>
+      <c r="U9">
+        <v>13.3</v>
+      </c>
+      <c r="V9">
+        <v>0.1038251366120219</v>
+      </c>
+      <c r="W9">
+        <v>0.3659942363112391</v>
+      </c>
+      <c r="X9">
+        <v>0.07213017887356805</v>
+      </c>
+      <c r="Y9">
+        <v>0.2938640574376711</v>
+      </c>
+      <c r="Z9">
+        <v>3.420306296086216</v>
+      </c>
+      <c r="AA9">
+        <v>0.7504254112308563</v>
+      </c>
+      <c r="AB9">
+        <v>0.07196772003692435</v>
+      </c>
+      <c r="AC9">
+        <v>0.678457691193932</v>
+      </c>
+      <c r="AD9">
+        <v>0.726</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0.726</v>
+      </c>
+      <c r="AG9">
+        <v>-12.574</v>
+      </c>
+      <c r="AH9">
+        <v>0.005635508360113642</v>
+      </c>
+      <c r="AI9">
+        <v>0.01914254073722512</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.1088412997939858</v>
+      </c>
+      <c r="AK9">
+        <v>-0.5105985543734265</v>
+      </c>
+      <c r="AL9">
+        <v>0.09</v>
+      </c>
+      <c r="AM9">
+        <v>-0.627</v>
+      </c>
+      <c r="AN9">
+        <v>0.0378125</v>
+      </c>
+      <c r="AO9">
+        <v>210</v>
+      </c>
+      <c r="AP9">
+        <v>-0.6548958333333335</v>
+      </c>
+      <c r="AQ9">
+        <v>-30.14354066985646</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Liontrust Asset Management PLC (LSE:LIO)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.116</v>
+      </c>
+      <c r="E10">
+        <v>-0.0766</v>
+      </c>
+      <c r="F10">
+        <v>-0.123</v>
+      </c>
+      <c r="G10">
+        <v>0.260132340777502</v>
+      </c>
+      <c r="H10">
+        <v>0.260132340777502</v>
+      </c>
+      <c r="I10">
+        <v>0.1699751861042184</v>
+      </c>
+      <c r="J10">
+        <v>0.1125511367446851</v>
+      </c>
+      <c r="K10">
+        <v>19.5</v>
+      </c>
+      <c r="L10">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="M10">
+        <v>61.7</v>
+      </c>
+      <c r="N10">
+        <v>0.1620273109243698</v>
+      </c>
+      <c r="O10">
+        <v>3.164102564102564</v>
+      </c>
+      <c r="P10">
+        <v>61.7</v>
+      </c>
+      <c r="Q10">
+        <v>0.1620273109243698</v>
+      </c>
+      <c r="R10">
+        <v>3.164102564102564</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>118.6</v>
+      </c>
+      <c r="V10">
+        <v>0.3114495798319327</v>
+      </c>
+      <c r="W10">
+        <v>0.08875739644970415</v>
+      </c>
+      <c r="X10">
+        <v>0.07212356064334327</v>
+      </c>
+      <c r="Y10">
+        <v>0.01663383580636088</v>
+      </c>
+      <c r="Z10">
+        <v>3.90882638215325</v>
+      </c>
+      <c r="AA10">
+        <v>0.4399428526489633</v>
+      </c>
+      <c r="AB10">
+        <v>0.07198465282724401</v>
+      </c>
+      <c r="AC10">
+        <v>0.3679581998217193</v>
+      </c>
+      <c r="AD10">
+        <v>2.03</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>2.03</v>
+      </c>
+      <c r="AG10">
+        <v>-116.57</v>
+      </c>
+      <c r="AH10">
+        <v>0.005302614737611995</v>
+      </c>
+      <c r="AI10">
+        <v>0.01009799532408098</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.4411686788025583</v>
+      </c>
+      <c r="AK10">
+        <v>-1.414169598447167</v>
+      </c>
+      <c r="AL10">
+        <v>0.076</v>
+      </c>
+      <c r="AM10">
+        <v>-2.354</v>
+      </c>
+      <c r="AN10">
+        <v>0.03752310536044362</v>
+      </c>
+      <c r="AO10">
+        <v>540.7894736842105</v>
+      </c>
+      <c r="AP10">
+        <v>-2.154713493530499</v>
+      </c>
+      <c r="AQ10">
+        <v>-17.45964316057774</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Impax Asset Management Group Plc (AIM:IPX)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.182</v>
+      </c>
+      <c r="E11">
+        <v>0.181</v>
+      </c>
+      <c r="G11">
+        <v>0.3158333333333334</v>
+      </c>
+      <c r="H11">
+        <v>0.3065789473684211</v>
+      </c>
+      <c r="I11">
+        <v>0.2881578947368421</v>
+      </c>
+      <c r="J11">
+        <v>0.2148006258023106</v>
+      </c>
+      <c r="K11">
+        <v>48.9</v>
+      </c>
+      <c r="L11">
+        <v>0.2144736842105263</v>
+      </c>
+      <c r="M11">
+        <v>60</v>
+      </c>
+      <c r="N11">
+        <v>0.1518602885345482</v>
+      </c>
+      <c r="O11">
+        <v>1.226993865030675</v>
+      </c>
+      <c r="P11">
+        <v>48.7</v>
+      </c>
+      <c r="Q11">
+        <v>0.123259934193875</v>
+      </c>
+      <c r="R11">
+        <v>0.9959100204498978</v>
+      </c>
+      <c r="S11">
+        <v>11.3</v>
+      </c>
+      <c r="T11">
+        <v>0.1883333333333333</v>
+      </c>
+      <c r="U11">
+        <v>33.9</v>
+      </c>
+      <c r="V11">
+        <v>0.08580106302201973</v>
+      </c>
+      <c r="W11">
+        <v>0.2990825688073395</v>
+      </c>
+      <c r="X11">
+        <v>0.07253633988836555</v>
+      </c>
+      <c r="Y11">
+        <v>0.2265462289189739</v>
+      </c>
+      <c r="Z11">
+        <v>2.032085561497326</v>
+      </c>
+      <c r="AA11">
+        <v>0.4364932502934655</v>
+      </c>
+      <c r="AB11">
+        <v>0.07185389272468802</v>
+      </c>
+      <c r="AC11">
+        <v>0.3646393575687775</v>
+      </c>
+      <c r="AD11">
+        <v>10.4</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>10.4</v>
+      </c>
+      <c r="AG11">
+        <v>-23.5</v>
+      </c>
+      <c r="AH11">
+        <v>0.02564734895191122</v>
+      </c>
+      <c r="AI11">
+        <v>0.05588393336915637</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.06324004305705058</v>
+      </c>
+      <c r="AK11">
+        <v>-0.1544021024967148</v>
+      </c>
+      <c r="AL11">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="AM11">
+        <v>-3.872</v>
+      </c>
+      <c r="AN11">
+        <v>0.1487839771101574</v>
+      </c>
+      <c r="AO11">
+        <v>117.741935483871</v>
+      </c>
+      <c r="AP11">
+        <v>-0.3361945636623748</v>
+      </c>
+      <c r="AQ11">
+        <v>-16.96797520661157</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>City of London Investment Group Plc (LSE:CLIG)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.115</v>
+      </c>
+      <c r="E12">
+        <v>0.0901</v>
+      </c>
+      <c r="G12">
+        <v>0.4014388489208633</v>
+      </c>
+      <c r="H12">
+        <v>0.4014388489208633</v>
+      </c>
+      <c r="I12">
+        <v>0.316546762589928</v>
+      </c>
+      <c r="J12">
+        <v>0.2393709810912332</v>
+      </c>
+      <c r="K12">
+        <v>17.1</v>
+      </c>
+      <c r="L12">
+        <v>0.2460431654676259</v>
+      </c>
+      <c r="M12">
+        <v>21.22</v>
+      </c>
+      <c r="N12">
+        <v>0.08783112582781456</v>
+      </c>
+      <c r="O12">
+        <v>1.24093567251462</v>
+      </c>
+      <c r="P12">
+        <v>19.9</v>
+      </c>
+      <c r="Q12">
+        <v>0.08236754966887416</v>
+      </c>
+      <c r="R12">
+        <v>1.163742690058479</v>
+      </c>
+      <c r="S12">
+        <v>1.32</v>
+      </c>
+      <c r="T12">
+        <v>0.06220546654099907</v>
+      </c>
+      <c r="U12">
+        <v>33.7</v>
+      </c>
+      <c r="V12">
+        <v>0.1394867549668874</v>
+      </c>
+      <c r="W12">
+        <v>0.109967845659164</v>
+      </c>
+      <c r="X12">
+        <v>0.07248510397409572</v>
+      </c>
+      <c r="Y12">
+        <v>0.03748274168506828</v>
+      </c>
+      <c r="Z12">
+        <v>1.757269279393173</v>
+      </c>
+      <c r="AA12">
+        <v>0.4206392714498282</v>
+      </c>
+      <c r="AB12">
+        <v>0.0718090172249576</v>
+      </c>
+      <c r="AC12">
+        <v>0.3488302542248706</v>
+      </c>
+      <c r="AD12">
+        <v>5.73</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>5.73</v>
+      </c>
+      <c r="AG12">
+        <v>-27.97</v>
+      </c>
+      <c r="AH12">
+        <v>0.02316742813245462</v>
+      </c>
+      <c r="AI12">
+        <v>0.03596309546224817</v>
+      </c>
+      <c r="AJ12">
+        <v>-0.1309273042175725</v>
+      </c>
+      <c r="AK12">
+        <v>-0.2226379049590066</v>
+      </c>
+      <c r="AL12">
+        <v>0.381</v>
+      </c>
+      <c r="AM12">
+        <v>-1.079</v>
+      </c>
+      <c r="AN12">
+        <v>0.2053763440860215</v>
+      </c>
+      <c r="AO12">
+        <v>57.74278215223097</v>
+      </c>
+      <c r="AP12">
+        <v>-1.002508960573477</v>
+      </c>
+      <c r="AQ12">
+        <v>-20.38924930491196</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sure Ventures Plc (LSE:SURE)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0.8694444444444444</v>
+      </c>
+      <c r="J13">
+        <v>0.8694444444444444</v>
+      </c>
+      <c r="K13">
+        <v>2.93</v>
+      </c>
+      <c r="L13">
+        <v>0.8138888888888889</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>-0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0.017</v>
+      </c>
+      <c r="V13">
+        <v>0.002165605095541401</v>
+      </c>
+      <c r="W13">
+        <v>0.3020618556701031</v>
+      </c>
+      <c r="X13">
+        <v>0.07349666890424662</v>
+      </c>
+      <c r="Y13">
+        <v>0.2285651867658565</v>
+      </c>
+      <c r="Z13">
+        <v>0.3654451324738606</v>
+      </c>
+      <c r="AA13">
+        <v>0.3177342401786621</v>
+      </c>
+      <c r="AB13">
+        <v>0.07138593646581839</v>
+      </c>
+      <c r="AC13">
+        <v>0.2463483037128437</v>
+      </c>
+      <c r="AD13">
+        <v>0.59</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0.59</v>
+      </c>
+      <c r="AG13">
+        <v>0.573</v>
+      </c>
+      <c r="AH13">
+        <v>0.06990521327014218</v>
+      </c>
+      <c r="AI13">
+        <v>0.03989181879648411</v>
+      </c>
+      <c r="AJ13">
+        <v>0.06802801852071708</v>
+      </c>
+      <c r="AK13">
+        <v>0.03878697624043864</v>
+      </c>
+      <c r="AL13">
+        <v>0.042</v>
+      </c>
+      <c r="AM13">
+        <v>0.042</v>
+      </c>
+      <c r="AO13">
+        <v>74.52380952380952</v>
+      </c>
+      <c r="AQ13">
+        <v>74.52380952380952</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kingswood Holdings Limited (AIM:KWG)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.627</v>
+      </c>
+      <c r="G14">
+        <v>0.1777970511708586</v>
+      </c>
+      <c r="H14">
+        <v>0.1777970511708586</v>
+      </c>
+      <c r="I14">
+        <v>0.1300954032957502</v>
+      </c>
+      <c r="J14">
+        <v>0.1300954032957502</v>
+      </c>
+      <c r="K14">
+        <v>-18.4</v>
+      </c>
+      <c r="L14">
+        <v>-0.1595836947094536</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>19.5</v>
+      </c>
+      <c r="V14">
+        <v>0.2213393870601589</v>
+      </c>
+      <c r="W14">
+        <v>1.821782178217822</v>
+      </c>
+      <c r="X14">
+        <v>0.09447280283754464</v>
+      </c>
+      <c r="Y14">
+        <v>1.727309375380277</v>
+      </c>
+      <c r="Z14">
+        <v>2.044326241134752</v>
+      </c>
+      <c r="AA14">
+        <v>0.2659574468085106</v>
+      </c>
+      <c r="AB14">
+        <v>0.06959184767978738</v>
+      </c>
+      <c r="AC14">
+        <v>0.1963655991287233</v>
+      </c>
+      <c r="AD14">
+        <v>100.6</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>100.6</v>
+      </c>
+      <c r="AG14">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="AH14">
+        <v>0.5331213566507684</v>
+      </c>
+      <c r="AI14">
+        <v>0.5872737886748394</v>
+      </c>
+      <c r="AJ14">
+        <v>0.4793144208037825</v>
+      </c>
+      <c r="AK14">
+        <v>0.5342555994729907</v>
+      </c>
+      <c r="AL14">
+        <v>13.1</v>
+      </c>
+      <c r="AM14">
+        <v>13.1</v>
+      </c>
+      <c r="AN14">
+        <v>4.72300469483568</v>
+      </c>
+      <c r="AO14">
+        <v>1.145038167938931</v>
+      </c>
+      <c r="AP14">
+        <v>3.807511737089202</v>
+      </c>
+      <c r="AQ14">
+        <v>1.145038167938931</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rathbones Group Plc (LSE:RAT)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.192</v>
+      </c>
+      <c r="E15">
+        <v>0.202</v>
+      </c>
+      <c r="F15">
+        <v>0.0326</v>
+      </c>
+      <c r="G15">
+        <v>0.2475585405699764</v>
+      </c>
+      <c r="H15">
+        <v>0.2442367035759666</v>
+      </c>
+      <c r="I15">
+        <v>0.2597567616627337</v>
+      </c>
+      <c r="J15">
+        <v>0.169637068840969</v>
+      </c>
+      <c r="K15">
+        <v>80</v>
+      </c>
+      <c r="L15">
+        <v>0.07260845888546016</v>
+      </c>
+      <c r="M15">
+        <v>102.9</v>
+      </c>
+      <c r="N15">
+        <v>0.04727339550696008</v>
+      </c>
+      <c r="O15">
+        <v>1.28625</v>
+      </c>
+      <c r="P15">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="Q15">
+        <v>0.03670694170073966</v>
+      </c>
+      <c r="R15">
+        <v>0.99875</v>
+      </c>
+      <c r="S15">
+        <v>23</v>
+      </c>
+      <c r="T15">
+        <v>0.2235179786200194</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.1018070755917536</v>
+      </c>
+      <c r="X15">
+        <v>0.07324734182334926</v>
+      </c>
+      <c r="Y15">
+        <v>0.02855973376840437</v>
+      </c>
+      <c r="Z15">
+        <v>1.557754842358264</v>
+      </c>
+      <c r="AA15">
+        <v>0.2642529654304815</v>
+      </c>
+      <c r="AB15">
+        <v>0.07148641148720665</v>
+      </c>
+      <c r="AC15">
+        <v>0.1927665539432749</v>
+      </c>
+      <c r="AD15">
+        <v>136</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>136</v>
+      </c>
+      <c r="AG15">
+        <v>136</v>
+      </c>
+      <c r="AH15">
+        <v>0.05880572491027804</v>
+      </c>
+      <c r="AI15">
+        <v>0.07296137339055794</v>
+      </c>
+      <c r="AJ15">
+        <v>0.05880572491027804</v>
+      </c>
+      <c r="AK15">
+        <v>0.07296137339055794</v>
+      </c>
+      <c r="AL15">
+        <v>95.8</v>
+      </c>
+      <c r="AM15">
+        <v>95.8</v>
+      </c>
+      <c r="AN15">
+        <v>0.4</v>
+      </c>
+      <c r="AO15">
+        <v>2.987473903966597</v>
+      </c>
+      <c r="AP15">
+        <v>0.4</v>
+      </c>
+      <c r="AQ15">
+        <v>2.987473903966597</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B.P. Marsh &amp; Partners PLC (AIM:BPM)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.34</v>
+      </c>
+      <c r="E16">
+        <v>0.354</v>
+      </c>
+      <c r="G16">
+        <v>0.6598802395209581</v>
+      </c>
+      <c r="H16">
+        <v>0.6598802395209581</v>
+      </c>
+      <c r="I16">
+        <v>0.8467065868263474</v>
+      </c>
+      <c r="J16">
+        <v>0.7946104516750946</v>
+      </c>
+      <c r="K16">
+        <v>68.8</v>
+      </c>
+      <c r="L16">
+        <v>0.8239520958083832</v>
+      </c>
+      <c r="M16">
+        <v>5.973</v>
+      </c>
+      <c r="N16">
+        <v>0.01776092774308653</v>
+      </c>
+      <c r="O16">
+        <v>0.08681686046511627</v>
+      </c>
+      <c r="P16">
+        <v>5.09</v>
+      </c>
+      <c r="Q16">
+        <v>0.01513529586678561</v>
+      </c>
+      <c r="R16">
+        <v>0.07398255813953489</v>
+      </c>
+      <c r="S16">
+        <v>0.883</v>
+      </c>
+      <c r="T16">
+        <v>0.1478319102628495</v>
+      </c>
+      <c r="U16">
+        <v>103</v>
+      </c>
+      <c r="V16">
+        <v>0.3062741599762117</v>
+      </c>
+      <c r="W16">
+        <v>0.2628964463125716</v>
+      </c>
+      <c r="X16">
+        <v>0.07205656512791674</v>
+      </c>
+      <c r="Y16">
+        <v>0.1908398811846549</v>
+      </c>
+      <c r="Z16">
+        <v>0.3247750883893879</v>
+      </c>
+      <c r="AA16">
+        <v>0.2580696796779103</v>
+      </c>
+      <c r="AB16">
+        <v>0.07200135198044172</v>
+      </c>
+      <c r="AC16">
+        <v>0.1860683276974686</v>
+      </c>
+      <c r="AD16">
+        <v>0.647</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0.647</v>
+      </c>
+      <c r="AG16">
+        <v>-102.353</v>
+      </c>
+      <c r="AH16">
+        <v>0.001920183292921439</v>
+      </c>
+      <c r="AI16">
+        <v>0.001988645968765656</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.4375050759360026</v>
+      </c>
+      <c r="AK16">
+        <v>-0.4603300246911359</v>
+      </c>
+      <c r="AL16">
+        <v>0.128</v>
+      </c>
+      <c r="AM16">
+        <v>-2.472</v>
+      </c>
+      <c r="AN16">
+        <v>0.009151343705799151</v>
+      </c>
+      <c r="AO16">
+        <v>552.34375</v>
+      </c>
+      <c r="AP16">
+        <v>-1.447708628005657</v>
+      </c>
+      <c r="AQ16">
+        <v>-28.60032362459547</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>St. James's Place plc (LSE:STJ)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.319</v>
+      </c>
+      <c r="F17">
+        <v>0.09</v>
+      </c>
+      <c r="G17">
+        <v>0.01575723929387724</v>
+      </c>
+      <c r="H17">
+        <v>0.01575723929387724</v>
+      </c>
+      <c r="I17">
+        <v>0.02243693855975998</v>
+      </c>
+      <c r="J17">
+        <v>0.01121846927987999</v>
+      </c>
+      <c r="K17">
+        <v>-8.34</v>
+      </c>
+      <c r="L17">
+        <v>-0.0002462806891134486</v>
+      </c>
+      <c r="M17">
+        <v>169.25</v>
+      </c>
+      <c r="N17">
+        <v>0.02885369429574823</v>
+      </c>
+      <c r="O17">
+        <v>-20.29376498800959</v>
+      </c>
+      <c r="P17">
+        <v>164.7</v>
+      </c>
+      <c r="Q17">
+        <v>0.02807801152442974</v>
+      </c>
+      <c r="R17">
+        <v>-19.74820143884892</v>
+      </c>
+      <c r="S17">
+        <v>4.550000000000011</v>
+      </c>
+      <c r="T17">
+        <v>0.02688330871491883</v>
+      </c>
+      <c r="U17">
+        <v>441.6</v>
+      </c>
+      <c r="V17">
+        <v>0.07528384875038358</v>
+      </c>
+      <c r="W17">
+        <v>-0.005267479315354008</v>
+      </c>
+      <c r="X17">
+        <v>0.07459432290181424</v>
+      </c>
+      <c r="Y17">
+        <v>-0.07986180221716825</v>
+      </c>
+      <c r="Z17">
+        <v>21.15297645074646</v>
+      </c>
+      <c r="AA17">
+        <v>0.237304016490724</v>
+      </c>
+      <c r="AB17">
+        <v>0.07127439271548976</v>
+      </c>
+      <c r="AC17">
+        <v>0.1660296237752342</v>
+      </c>
+      <c r="AD17">
+        <v>768.3</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>768.3</v>
+      </c>
+      <c r="AG17">
+        <v>326.6999999999999</v>
+      </c>
+      <c r="AH17">
+        <v>0.1158107354426373</v>
+      </c>
+      <c r="AI17">
+        <v>0.3552832369942197</v>
+      </c>
+      <c r="AJ17">
+        <v>0.05275736778360919</v>
+      </c>
+      <c r="AK17">
+        <v>0.1898425242605613</v>
+      </c>
+      <c r="AL17">
+        <v>21.9</v>
+      </c>
+      <c r="AM17">
+        <v>-39.8</v>
+      </c>
+      <c r="AN17">
+        <v>0.9927639229874661</v>
+      </c>
+      <c r="AO17">
+        <v>34.69406392694064</v>
+      </c>
+      <c r="AP17">
+        <v>0.4221475642847912</v>
+      </c>
+      <c r="AQ17">
+        <v>-19.09045226130653</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3i Group plc (LSE:III)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.253</v>
+      </c>
+      <c r="E18">
+        <v>0.268</v>
+      </c>
+      <c r="F18">
+        <v>0.131</v>
+      </c>
+      <c r="G18">
+        <v>0.8394333350737048</v>
+      </c>
+      <c r="H18">
+        <v>0.8394333350737048</v>
+      </c>
+      <c r="I18">
+        <v>0.9608068361788406</v>
+      </c>
+      <c r="J18">
+        <v>0.9603509292523251</v>
+      </c>
+      <c r="K18">
+        <v>5645.4</v>
+      </c>
+      <c r="L18">
+        <v>0.9825092674776797</v>
+      </c>
+      <c r="M18">
+        <v>786.8</v>
+      </c>
+      <c r="N18">
+        <v>0.01828500248664879</v>
+      </c>
+      <c r="O18">
+        <v>0.1393701066354908</v>
+      </c>
+      <c r="P18">
+        <v>786.8</v>
+      </c>
+      <c r="Q18">
+        <v>0.01828500248664879</v>
+      </c>
+      <c r="R18">
+        <v>0.1393701066354908</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>494.6</v>
+      </c>
+      <c r="V18">
+        <v>0.01149435972279676</v>
+      </c>
+      <c r="W18">
+        <v>0.2535583232650788</v>
+      </c>
+      <c r="X18">
+        <v>0.07277641801144429</v>
+      </c>
+      <c r="Y18">
+        <v>0.1807819052536345</v>
+      </c>
+      <c r="Z18">
+        <v>0.242294798540977</v>
+      </c>
+      <c r="AA18">
+        <v>0.2326880349318322</v>
+      </c>
+      <c r="AB18">
+        <v>0.07178027212278756</v>
+      </c>
+      <c r="AC18">
+        <v>0.1609077628090446</v>
+      </c>
+      <c r="AD18">
+        <v>1658</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>1658</v>
+      </c>
+      <c r="AG18">
+        <v>1163.4</v>
+      </c>
+      <c r="AH18">
+        <v>0.03710184882674913</v>
+      </c>
+      <c r="AI18">
+        <v>0.05347938559991743</v>
+      </c>
+      <c r="AJ18">
+        <v>0.02632531701709765</v>
+      </c>
+      <c r="AK18">
+        <v>0.03813425986626459</v>
+      </c>
+      <c r="AL18">
+        <v>89.8</v>
+      </c>
+      <c r="AM18">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="AN18">
+        <v>0.3000687733014805</v>
+      </c>
+      <c r="AO18">
+        <v>61.47772828507795</v>
+      </c>
+      <c r="AP18">
+        <v>0.2105548919535238</v>
+      </c>
+      <c r="AQ18">
+        <v>76.25276243093921</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brooks Macdonald Group plc (AIM:BRK)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.0396</v>
+      </c>
+      <c r="E19">
+        <v>0.0341</v>
+      </c>
+      <c r="G19">
+        <v>0.2432449105490438</v>
+      </c>
+      <c r="H19">
+        <v>0.2307217766810611</v>
+      </c>
+      <c r="I19">
+        <v>0.1782850092535472</v>
+      </c>
+      <c r="J19">
+        <v>0.09920893712204192</v>
+      </c>
+      <c r="K19">
+        <v>8.16</v>
+      </c>
+      <c r="L19">
+        <v>0.05033929673041333</v>
+      </c>
+      <c r="M19">
+        <v>18.02</v>
+      </c>
+      <c r="N19">
+        <v>0.05342425140824192</v>
+      </c>
+      <c r="O19">
+        <v>2.208333333333333</v>
+      </c>
+      <c r="P19">
+        <v>15.3</v>
+      </c>
+      <c r="Q19">
+        <v>0.04536021345982805</v>
+      </c>
+      <c r="R19">
+        <v>1.875</v>
+      </c>
+      <c r="S19">
+        <v>2.719999999999999</v>
+      </c>
+      <c r="T19">
+        <v>0.150943396226415</v>
+      </c>
+      <c r="U19">
+        <v>56.5</v>
+      </c>
+      <c r="V19">
+        <v>0.1675066706196264</v>
+      </c>
+      <c r="W19">
+        <v>0.0408</v>
+      </c>
+      <c r="X19">
+        <v>0.07229973219347213</v>
+      </c>
+      <c r="Y19">
+        <v>-0.03149973219347213</v>
+      </c>
+      <c r="Z19">
+        <v>2.278925910305075</v>
+      </c>
+      <c r="AA19">
+        <v>0.2260898173412483</v>
+      </c>
+      <c r="AB19">
+        <v>0.07189120056732494</v>
+      </c>
+      <c r="AC19">
+        <v>0.1541986167739233</v>
+      </c>
+      <c r="AD19">
+        <v>4.82</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>4.82</v>
+      </c>
+      <c r="AG19">
+        <v>-51.68</v>
+      </c>
+      <c r="AH19">
+        <v>0.01408862387466386</v>
+      </c>
+      <c r="AI19">
+        <v>0.02442732617068721</v>
+      </c>
+      <c r="AJ19">
+        <v>-0.1809397101043344</v>
+      </c>
+      <c r="AK19">
+        <v>-0.3669933248118165</v>
+      </c>
+      <c r="AL19">
+        <v>0.246</v>
+      </c>
+      <c r="AM19">
+        <v>-3.614</v>
+      </c>
+      <c r="AN19">
+        <v>0.1288770053475936</v>
+      </c>
+      <c r="AO19">
+        <v>117.479674796748</v>
+      </c>
+      <c r="AP19">
+        <v>-1.381818181818182</v>
+      </c>
+      <c r="AQ19">
+        <v>-7.996679579413392</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>London Finance &amp; Investment Group P.L.C. (LSE:LFI)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.339</v>
+      </c>
+      <c r="E20">
+        <v>0.361</v>
+      </c>
+      <c r="G20">
+        <v>0.8164983164983164</v>
+      </c>
+      <c r="H20">
+        <v>0.8164983164983164</v>
+      </c>
+      <c r="I20">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="J20">
+        <v>0.7739285714285714</v>
+      </c>
+      <c r="K20">
+        <v>5.35</v>
+      </c>
+      <c r="L20">
+        <v>0.9006734006734005</v>
+      </c>
+      <c r="M20">
+        <v>0.473</v>
+      </c>
+      <c r="N20">
+        <v>0.01732600732600733</v>
+      </c>
+      <c r="O20">
+        <v>0.08841121495327103</v>
+      </c>
+      <c r="P20">
+        <v>0.473</v>
+      </c>
+      <c r="Q20">
+        <v>0.01732600732600733</v>
+      </c>
+      <c r="R20">
+        <v>0.08841121495327103</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>12</v>
+      </c>
+      <c r="V20">
+        <v>0.4395604395604396</v>
+      </c>
+      <c r="W20">
+        <v>0.2276595744680851</v>
+      </c>
+      <c r="X20">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y20">
+        <v>0.1556408405641555</v>
+      </c>
+      <c r="Z20">
+        <v>0.2708371329564107</v>
+      </c>
+      <c r="AA20">
+        <v>0.209608595398765</v>
+      </c>
+      <c r="AB20">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC20">
+        <v>0.1375898614948354</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>-12</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>-0.7843137254901961</v>
+      </c>
+      <c r="AK20">
+        <v>-0.7407407407407408</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-0.008</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>-2.474226804123711</v>
+      </c>
+      <c r="AQ20">
+        <v>-605</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Volvere plc (AIM:VLE)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.168</v>
+      </c>
+      <c r="E21">
+        <v>-0.322</v>
+      </c>
+      <c r="G21">
+        <v>0.07903780068728522</v>
+      </c>
+      <c r="H21">
+        <v>0.07903780068728522</v>
+      </c>
+      <c r="I21">
+        <v>0.09690721649484535</v>
+      </c>
+      <c r="J21">
+        <v>0.06960739591886383</v>
+      </c>
+      <c r="K21">
+        <v>4.12</v>
+      </c>
+      <c r="L21">
+        <v>0.07079037800687285</v>
+      </c>
+      <c r="M21">
+        <v>1.86</v>
+      </c>
+      <c r="N21">
+        <v>0.0420814479638009</v>
+      </c>
+      <c r="O21">
+        <v>0.4514563106796117</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>-0</v>
+      </c>
+      <c r="S21">
+        <v>1.86</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>28</v>
+      </c>
+      <c r="V21">
+        <v>0.6334841628959276</v>
+      </c>
+      <c r="W21">
+        <v>0.09880095923261391</v>
+      </c>
+      <c r="X21">
+        <v>0.07274835025464979</v>
+      </c>
+      <c r="Y21">
+        <v>0.02605260897796412</v>
+      </c>
+      <c r="Z21">
+        <v>3.004646360351058</v>
+      </c>
+      <c r="AA21">
+        <v>0.2091456088011293</v>
+      </c>
+      <c r="AB21">
+        <v>0.07185587084970414</v>
+      </c>
+      <c r="AC21">
+        <v>0.1372897379514252</v>
+      </c>
+      <c r="AD21">
+        <v>1.64</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>1.64</v>
+      </c>
+      <c r="AG21">
+        <v>-26.36</v>
+      </c>
+      <c r="AH21">
+        <v>0.03577661431064572</v>
+      </c>
+      <c r="AI21">
+        <v>0.03251387787470262</v>
+      </c>
+      <c r="AJ21">
+        <v>-1.477578475336323</v>
+      </c>
+      <c r="AK21">
+        <v>-1.174688057040998</v>
+      </c>
+      <c r="AL21">
+        <v>0.227</v>
+      </c>
+      <c r="AM21">
+        <v>-1.123</v>
+      </c>
+      <c r="AN21">
+        <v>0.2523076923076923</v>
+      </c>
+      <c r="AO21">
+        <v>24.84581497797357</v>
+      </c>
+      <c r="AP21">
+        <v>-4.055384615384615</v>
+      </c>
+      <c r="AQ21">
+        <v>-5.022261798753339</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Janus Henderson Group plc (NYSE:JHG)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>0.0178</v>
+      </c>
+      <c r="E22">
+        <v>-0.00672</v>
+      </c>
+      <c r="F22">
+        <v>0.0476</v>
+      </c>
+      <c r="G22">
+        <v>0.2171080826262107</v>
+      </c>
+      <c r="H22">
+        <v>0.2171080826262107</v>
+      </c>
+      <c r="I22">
+        <v>0.2579898923265542</v>
+      </c>
+      <c r="J22">
+        <v>0.1951905436371474</v>
+      </c>
+      <c r="K22">
+        <v>408.4</v>
+      </c>
+      <c r="L22">
+        <v>0.1750235707551213</v>
+      </c>
+      <c r="M22">
+        <v>549.9000000000001</v>
+      </c>
+      <c r="N22">
+        <v>0.0819034852546917</v>
+      </c>
+      <c r="O22">
+        <v>1.346474045053869</v>
+      </c>
+      <c r="P22">
+        <v>252.8</v>
+      </c>
+      <c r="Q22">
+        <v>0.03765266607089664</v>
+      </c>
+      <c r="R22">
+        <v>0.6190009794319296</v>
+      </c>
+      <c r="S22">
+        <v>297.1000000000001</v>
+      </c>
+      <c r="T22">
+        <v>0.5402800509183489</v>
+      </c>
+      <c r="U22">
+        <v>1504.8</v>
+      </c>
+      <c r="V22">
+        <v>0.2241286863270777</v>
+      </c>
+      <c r="W22">
+        <v>0.09165376242734352</v>
+      </c>
+      <c r="X22">
+        <v>0.07426991307548753</v>
+      </c>
+      <c r="Y22">
+        <v>0.017383849351856</v>
+      </c>
+      <c r="Z22">
+        <v>0.9597998260926122</v>
+      </c>
+      <c r="AA22">
+        <v>0.1873438498378565</v>
+      </c>
+      <c r="AB22">
+        <v>0.07144326180470691</v>
+      </c>
+      <c r="AC22">
+        <v>0.1159005880331496</v>
+      </c>
+      <c r="AD22">
+        <v>698.6</v>
+      </c>
+      <c r="AE22">
+        <v>70.0319262260921</v>
+      </c>
+      <c r="AF22">
+        <v>768.6319262260921</v>
+      </c>
+      <c r="AG22">
+        <v>-736.1680737739078</v>
+      </c>
+      <c r="AH22">
+        <v>0.102722134912462</v>
+      </c>
+      <c r="AI22">
+        <v>0.1303797539892098</v>
+      </c>
+      <c r="AJ22">
+        <v>-0.1231496774849378</v>
+      </c>
+      <c r="AK22">
+        <v>-0.1676717277413549</v>
+      </c>
+      <c r="AL22">
+        <v>14</v>
+      </c>
+      <c r="AM22">
+        <v>-74.7</v>
+      </c>
+      <c r="AN22">
+        <v>1.097047738693467</v>
+      </c>
+      <c r="AO22">
+        <v>42.27857142857142</v>
+      </c>
+      <c r="AP22">
+        <v>-1.156042829418825</v>
+      </c>
+      <c r="AQ22">
+        <v>-7.923694779116465</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>XPS Pensions Group plc (LSE:XPS)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.139</v>
+      </c>
+      <c r="E23">
+        <v>0.339</v>
+      </c>
+      <c r="F23">
+        <v>0.102</v>
+      </c>
+      <c r="G23">
+        <v>0.1825017088174983</v>
+      </c>
+      <c r="H23">
+        <v>0.1825017088174983</v>
+      </c>
+      <c r="I23">
+        <v>0.1917293233082707</v>
+      </c>
+      <c r="J23">
+        <v>0.1631571219930607</v>
+      </c>
+      <c r="K23">
+        <v>82.7</v>
+      </c>
+      <c r="L23">
+        <v>0.2826384142173616</v>
+      </c>
+      <c r="M23">
+        <v>38.2</v>
+      </c>
+      <c r="N23">
+        <v>0.04317359855334539</v>
+      </c>
+      <c r="O23">
+        <v>0.4619105199516324</v>
+      </c>
+      <c r="P23">
+        <v>27.8</v>
+      </c>
+      <c r="Q23">
+        <v>0.03141952983725136</v>
+      </c>
+      <c r="R23">
+        <v>0.3361547762998791</v>
+      </c>
+      <c r="S23">
+        <v>10.4</v>
+      </c>
+      <c r="T23">
+        <v>0.2722513089005236</v>
+      </c>
+      <c r="U23">
+        <v>12.8</v>
+      </c>
+      <c r="V23">
+        <v>0.01446654611211573</v>
+      </c>
+      <c r="W23">
+        <v>0.4791425260718424</v>
+      </c>
+      <c r="X23">
+        <v>0.07341219679026806</v>
+      </c>
+      <c r="Y23">
+        <v>0.4057303292815744</v>
+      </c>
+      <c r="Z23">
+        <v>1.099462668620599</v>
+      </c>
+      <c r="AA23">
+        <v>0.1793851647509472</v>
+      </c>
+      <c r="AB23">
+        <v>0.07159341806710801</v>
+      </c>
+      <c r="AC23">
+        <v>0.1077917466838392</v>
+      </c>
+      <c r="AD23">
+        <v>62.7</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>62.7</v>
+      </c>
+      <c r="AG23">
+        <v>49.90000000000001</v>
+      </c>
+      <c r="AH23">
+        <v>0.06617414248021108</v>
+      </c>
+      <c r="AI23">
+        <v>0.2040351448096323</v>
+      </c>
+      <c r="AJ23">
+        <v>0.05338611319139832</v>
+      </c>
+      <c r="AK23">
+        <v>0.1694397283531409</v>
+      </c>
+      <c r="AL23">
+        <v>3.7</v>
+      </c>
+      <c r="AM23">
+        <v>3.612</v>
+      </c>
+      <c r="AN23">
+        <v>0.9330357142857143</v>
+      </c>
+      <c r="AO23">
+        <v>15.16216216216216</v>
+      </c>
+      <c r="AP23">
+        <v>0.7425595238095238</v>
+      </c>
+      <c r="AQ23">
+        <v>15.53156146179402</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bridgepoint Group plc (LSE:BPT)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>0.215</v>
+      </c>
+      <c r="G24">
+        <v>0.3925514688873467</v>
+      </c>
+      <c r="H24">
+        <v>0.3925514688873467</v>
+      </c>
+      <c r="I24">
+        <v>0.3832986352070321</v>
+      </c>
+      <c r="J24">
+        <v>0.3079747020540529</v>
+      </c>
+      <c r="K24">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="L24">
+        <v>0.19176497802452</v>
+      </c>
+      <c r="M24">
+        <v>135.2</v>
+      </c>
+      <c r="N24">
+        <v>0.0364656381486676</v>
+      </c>
+      <c r="O24">
+        <v>1.630880579010856</v>
+      </c>
+      <c r="P24">
+        <v>88.8</v>
+      </c>
+      <c r="Q24">
+        <v>0.02395080375445032</v>
+      </c>
+      <c r="R24">
+        <v>1.071170084439083</v>
+      </c>
+      <c r="S24">
+        <v>46.39999999999999</v>
+      </c>
+      <c r="T24">
+        <v>0.3431952662721893</v>
+      </c>
+      <c r="U24">
+        <v>156.6</v>
+      </c>
+      <c r="V24">
+        <v>0.04223756608048333</v>
+      </c>
+      <c r="W24">
+        <v>0.0858889349357646</v>
+      </c>
+      <c r="X24">
+        <v>0.07272412788033399</v>
+      </c>
+      <c r="Y24">
+        <v>0.01316480705543062</v>
+      </c>
+      <c r="Z24">
+        <v>0.5787923416789397</v>
+      </c>
+      <c r="AA24">
+        <v>0.178253398979739</v>
+      </c>
+      <c r="AB24">
+        <v>0.07179615920460712</v>
+      </c>
+      <c r="AC24">
+        <v>0.1064572397751319</v>
+      </c>
+      <c r="AD24">
+        <v>133</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>133</v>
+      </c>
+      <c r="AG24">
+        <v>-23.59999999999999</v>
+      </c>
+      <c r="AH24">
+        <v>0.03463000572827162</v>
+      </c>
+      <c r="AI24">
+        <v>0.1270660170058278</v>
+      </c>
+      <c r="AJ24">
+        <v>-0.006406080347448424</v>
+      </c>
+      <c r="AK24">
+        <v>-0.02651387484552297</v>
+      </c>
+      <c r="AL24">
+        <v>6.32</v>
+      </c>
+      <c r="AM24">
+        <v>-4.58</v>
+      </c>
+      <c r="AN24">
+        <v>0.7604345340194396</v>
+      </c>
+      <c r="AO24">
+        <v>26.21835443037974</v>
+      </c>
+      <c r="AP24">
+        <v>-0.1349342481417953</v>
+      </c>
+      <c r="AQ24">
+        <v>-36.17903930131004</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>British &amp; American Investment Trust PLC (LSE:BAF)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0.6993243243243242</v>
+      </c>
+      <c r="J25">
+        <v>0.6993243243243242</v>
+      </c>
+      <c r="K25">
+        <v>1.97</v>
+      </c>
+      <c r="L25">
+        <v>0.6655405405405406</v>
+      </c>
+      <c r="M25">
+        <v>0.552</v>
+      </c>
+      <c r="N25">
+        <v>0.07350199733688416</v>
+      </c>
+      <c r="O25">
+        <v>0.2802030456852792</v>
+      </c>
+      <c r="P25">
+        <v>0.552</v>
+      </c>
+      <c r="Q25">
+        <v>0.07350199733688416</v>
+      </c>
+      <c r="R25">
+        <v>0.2802030456852792</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0.015</v>
+      </c>
+      <c r="V25">
+        <v>0.001997336884154461</v>
+      </c>
+      <c r="W25">
+        <v>-1.238993710691824</v>
+      </c>
+      <c r="X25">
+        <v>0.07610341015793726</v>
+      </c>
+      <c r="Y25">
+        <v>-1.315097120849761</v>
+      </c>
+      <c r="Z25">
+        <v>0.2318477324351845</v>
+      </c>
+      <c r="AA25">
+        <v>0.1621367588313621</v>
+      </c>
+      <c r="AB25">
+        <v>0.0712357719714745</v>
+      </c>
+      <c r="AC25">
+        <v>0.09090098685988761</v>
+      </c>
+      <c r="AD25">
+        <v>1.56</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>1.56</v>
+      </c>
+      <c r="AG25">
+        <v>1.545</v>
+      </c>
+      <c r="AH25">
+        <v>0.1719955898566704</v>
+      </c>
+      <c r="AI25">
+        <v>0.1125541125541125</v>
+      </c>
+      <c r="AJ25">
+        <v>0.1706239646604086</v>
+      </c>
+      <c r="AK25">
+        <v>0.1115926327193933</v>
+      </c>
+      <c r="AL25">
+        <v>0.131</v>
+      </c>
+      <c r="AM25">
+        <v>0.131</v>
+      </c>
+      <c r="AO25">
+        <v>15.80152671755725</v>
+      </c>
+      <c r="AQ25">
+        <v>15.80152671755725</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ashmore Group Plc (LSE:ASHM)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>-0.0922</v>
+      </c>
+      <c r="E26">
+        <v>-0.121</v>
+      </c>
+      <c r="F26">
+        <v>-0.08779999999999999</v>
+      </c>
+      <c r="G26">
+        <v>0.3916941973739941</v>
+      </c>
+      <c r="H26">
+        <v>0.3900889453621347</v>
+      </c>
+      <c r="I26">
+        <v>0.3850063532401525</v>
+      </c>
+      <c r="J26">
+        <v>0.29511604964239</v>
+      </c>
+      <c r="K26">
+        <v>118.4</v>
+      </c>
+      <c r="L26">
+        <v>0.5014824227022449</v>
+      </c>
+      <c r="M26">
+        <v>168.9</v>
+      </c>
+      <c r="N26">
+        <v>0.1272124726971454</v>
+      </c>
+      <c r="O26">
+        <v>1.42652027027027</v>
+      </c>
+      <c r="P26">
+        <v>151.5</v>
+      </c>
+      <c r="Q26">
+        <v>0.1141071025080967</v>
+      </c>
+      <c r="R26">
+        <v>1.279560810810811</v>
+      </c>
+      <c r="S26">
+        <v>17.40000000000001</v>
+      </c>
+      <c r="T26">
+        <v>0.1030195381882771</v>
+      </c>
+      <c r="U26">
+        <v>646.8</v>
+      </c>
+      <c r="V26">
+        <v>0.4871582435791217</v>
+      </c>
+      <c r="W26">
+        <v>0.1036596042724567</v>
+      </c>
+      <c r="X26">
+        <v>0.0721385517603445</v>
+      </c>
+      <c r="Y26">
+        <v>0.03152105251211215</v>
+      </c>
+      <c r="Z26">
+        <v>0.5475798408980218</v>
+      </c>
+      <c r="AA26">
+        <v>0.1615995995096326</v>
+      </c>
+      <c r="AB26">
+        <v>0.07197980846076803</v>
+      </c>
+      <c r="AC26">
+        <v>0.08961979104886457</v>
+      </c>
+      <c r="AD26">
+        <v>8.09</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>8.09</v>
+      </c>
+      <c r="AG26">
+        <v>-638.7099999999999</v>
+      </c>
+      <c r="AH26">
+        <v>0.006056341191354928</v>
+      </c>
+      <c r="AI26">
+        <v>0.007134730882184339</v>
+      </c>
+      <c r="AJ26">
+        <v>-0.9270236142759689</v>
+      </c>
+      <c r="AK26">
+        <v>-1.311277176702457</v>
+      </c>
+      <c r="AL26">
+        <v>0.379</v>
+      </c>
+      <c r="AM26">
+        <v>-49.021</v>
+      </c>
+      <c r="AN26">
+        <v>0.08783930510314876</v>
+      </c>
+      <c r="AO26">
+        <v>239.8416886543536</v>
+      </c>
+      <c r="AP26">
+        <v>-6.934961997828447</v>
+      </c>
+      <c r="AQ26">
+        <v>-1.85430733767161</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Law Debenture Corporation p.l.c. (LSE:LWDB)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>0.4370000000000001</v>
+      </c>
+      <c r="G27">
+        <v>0.422562893081761</v>
+      </c>
+      <c r="H27">
+        <v>0.422562893081761</v>
+      </c>
+      <c r="I27">
+        <v>0.7405660377358491</v>
+      </c>
+      <c r="J27">
+        <v>0.732081243310177</v>
+      </c>
+      <c r="K27">
+        <v>177.7</v>
+      </c>
+      <c r="L27">
+        <v>0.698506289308176</v>
+      </c>
+      <c r="M27">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="N27">
+        <v>0.0443089430894309</v>
+      </c>
+      <c r="O27">
+        <v>0.3680360157568937</v>
+      </c>
+      <c r="P27">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="Q27">
+        <v>0.0443089430894309</v>
+      </c>
+      <c r="R27">
+        <v>0.3680360157568937</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>34.5</v>
+      </c>
+      <c r="V27">
+        <v>0.0233739837398374</v>
+      </c>
+      <c r="W27">
+        <v>0.1720898702304862</v>
+      </c>
+      <c r="X27">
+        <v>0.0748684225126951</v>
+      </c>
+      <c r="Y27">
+        <v>0.09722144771779107</v>
+      </c>
+      <c r="Z27">
+        <v>0.2152830667682153</v>
+      </c>
+      <c r="AA27">
+        <v>0.1576046951833029</v>
+      </c>
+      <c r="AB27">
+        <v>0.07087294417233268</v>
+      </c>
+      <c r="AC27">
+        <v>0.08673175101097021</v>
+      </c>
+      <c r="AD27">
+        <v>213.9</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>213.9</v>
+      </c>
+      <c r="AG27">
+        <v>179.4</v>
+      </c>
+      <c r="AH27">
+        <v>0.1265755370140245</v>
+      </c>
+      <c r="AI27">
+        <v>0.1563710797572922</v>
+      </c>
+      <c r="AJ27">
+        <v>0.1083725987676694</v>
+      </c>
+      <c r="AK27">
+        <v>0.1345432728363582</v>
+      </c>
+      <c r="AL27">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="AM27">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="AN27">
+        <v>1.127569847127043</v>
+      </c>
+      <c r="AO27">
+        <v>21.8815331010453</v>
+      </c>
+      <c r="AP27">
+        <v>0.9457037427517133</v>
+      </c>
+      <c r="AQ27">
+        <v>21.8815331010453</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Man Group Plc (LSE:EMG)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.0745</v>
+      </c>
+      <c r="E28">
+        <v>0.0174</v>
+      </c>
+      <c r="F28">
+        <v>0.227</v>
+      </c>
+      <c r="G28">
+        <v>0.1899641577060932</v>
+      </c>
+      <c r="H28">
+        <v>0.1899641577060932</v>
+      </c>
+      <c r="I28">
+        <v>0.2186379928315412</v>
+      </c>
+      <c r="J28">
+        <v>0.1796560251173905</v>
+      </c>
+      <c r="K28">
+        <v>315</v>
+      </c>
+      <c r="L28">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="M28">
+        <v>256</v>
+      </c>
+      <c r="N28">
+        <v>0.08260729267505647</v>
+      </c>
+      <c r="O28">
+        <v>0.8126984126984127</v>
+      </c>
+      <c r="P28">
+        <v>190</v>
+      </c>
+      <c r="Q28">
+        <v>0.06131010003226847</v>
+      </c>
+      <c r="R28">
+        <v>0.6031746031746031</v>
+      </c>
+      <c r="S28">
+        <v>66</v>
+      </c>
+      <c r="T28">
+        <v>0.2578125</v>
+      </c>
+      <c r="U28">
+        <v>279</v>
+      </c>
+      <c r="V28">
+        <v>0.09002904162633107</v>
+      </c>
+      <c r="W28">
+        <v>0.2086092715231788</v>
+      </c>
+      <c r="X28">
+        <v>0.07505178201769491</v>
+      </c>
+      <c r="Y28">
+        <v>0.1335574895054839</v>
+      </c>
+      <c r="Z28">
+        <v>0.8348294434470377</v>
+      </c>
+      <c r="AA28">
+        <v>0.1499821394606581</v>
+      </c>
+      <c r="AB28">
+        <v>0.07115985449995946</v>
+      </c>
+      <c r="AC28">
+        <v>0.07882228496069865</v>
+      </c>
+      <c r="AD28">
+        <v>478</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>478</v>
+      </c>
+      <c r="AG28">
+        <v>199</v>
+      </c>
+      <c r="AH28">
+        <v>0.1336315348057031</v>
+      </c>
+      <c r="AI28">
+        <v>0.2304725168756027</v>
+      </c>
+      <c r="AJ28">
+        <v>0.06033959975742875</v>
+      </c>
+      <c r="AK28">
+        <v>0.1108635097493036</v>
+      </c>
+      <c r="AL28">
+        <v>25</v>
+      </c>
+      <c r="AM28">
+        <v>15</v>
+      </c>
+      <c r="AN28">
+        <v>1.38150289017341</v>
+      </c>
+      <c r="AO28">
+        <v>12.2</v>
+      </c>
+      <c r="AP28">
+        <v>0.5751445086705202</v>
+      </c>
+      <c r="AQ28">
+        <v>20.33333333333333</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rights and Issues Investment Trust Public Limited Company (LSE:RIII)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0.9391304347826087</v>
+      </c>
+      <c r="J29">
+        <v>0.9391304347826087</v>
+      </c>
+      <c r="K29">
+        <v>21.6</v>
+      </c>
+      <c r="L29">
+        <v>0.9391304347826087</v>
+      </c>
+      <c r="M29">
+        <v>18.41</v>
+      </c>
+      <c r="N29">
+        <v>0.1263555250514757</v>
+      </c>
+      <c r="O29">
+        <v>0.8523148148148147</v>
+      </c>
+      <c r="P29">
+        <v>3.01</v>
+      </c>
+      <c r="Q29">
+        <v>0.02065888812628689</v>
+      </c>
+      <c r="R29">
+        <v>0.1393518518518518</v>
+      </c>
+      <c r="S29">
+        <v>15.4</v>
+      </c>
+      <c r="T29">
+        <v>0.8365019011406845</v>
+      </c>
+      <c r="U29">
+        <v>5.22</v>
+      </c>
+      <c r="V29">
+        <v>0.03582704186684969</v>
+      </c>
+      <c r="W29">
+        <v>0.1239954075774971</v>
+      </c>
+      <c r="X29">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y29">
+        <v>0.05197667367356758</v>
+      </c>
+      <c r="Z29">
+        <v>0.1367745004757374</v>
+      </c>
+      <c r="AA29">
+        <v>0.1284490960989534</v>
+      </c>
+      <c r="AB29">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC29">
+        <v>0.05643036219502381</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>-5.22</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>-0.03715831435079726</v>
+      </c>
+      <c r="AK29">
+        <v>-0.03049421661409043</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pollen Street Group Limited (LSE:POLN)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>0.118</v>
+      </c>
+      <c r="E30">
+        <v>0.0864</v>
+      </c>
+      <c r="G30">
+        <v>0.5963636363636363</v>
+      </c>
+      <c r="H30">
+        <v>0.5963636363636363</v>
+      </c>
+      <c r="I30">
+        <v>0.6189090909090909</v>
+      </c>
+      <c r="J30">
+        <v>0.6020018061408789</v>
+      </c>
+      <c r="K30">
+        <v>58.8</v>
+      </c>
+      <c r="L30">
+        <v>0.4276363636363636</v>
+      </c>
+      <c r="M30">
+        <v>43.6</v>
+      </c>
+      <c r="N30">
+        <v>0.07523727351164798</v>
+      </c>
+      <c r="O30">
+        <v>0.7414965986394558</v>
+      </c>
+      <c r="P30">
+        <v>30.6</v>
+      </c>
+      <c r="Q30">
+        <v>0.05280414150129422</v>
+      </c>
+      <c r="R30">
+        <v>0.5204081632653061</v>
+      </c>
+      <c r="S30">
+        <v>13</v>
+      </c>
+      <c r="T30">
+        <v>0.2981651376146789</v>
+      </c>
+      <c r="U30">
+        <v>37.6</v>
+      </c>
+      <c r="V30">
+        <v>0.06488352027610009</v>
+      </c>
+      <c r="W30">
+        <v>0.07994561522773623</v>
+      </c>
+      <c r="X30">
+        <v>0.07773640861852682</v>
+      </c>
+      <c r="Y30">
+        <v>0.00220920660920941</v>
+      </c>
+      <c r="Z30">
+        <v>0.1878928669035256</v>
+      </c>
+      <c r="AA30">
+        <v>0.1131118452369102</v>
+      </c>
+      <c r="AB30">
+        <v>0.06997956380369523</v>
+      </c>
+      <c r="AC30">
+        <v>0.04313228143321493</v>
+      </c>
+      <c r="AD30">
+        <v>168.5</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>168.5</v>
+      </c>
+      <c r="AG30">
+        <v>130.9</v>
+      </c>
+      <c r="AH30">
+        <v>0.2252673796791444</v>
+      </c>
+      <c r="AI30">
+        <v>0.1854705558613098</v>
+      </c>
+      <c r="AJ30">
+        <v>0.1842623873873874</v>
+      </c>
+      <c r="AK30">
+        <v>0.150304282925709</v>
+      </c>
+      <c r="AL30">
+        <v>35.5</v>
+      </c>
+      <c r="AM30">
+        <v>35.5</v>
+      </c>
+      <c r="AN30">
+        <v>1.961583236321304</v>
+      </c>
+      <c r="AO30">
+        <v>2.397183098591549</v>
+      </c>
+      <c r="AP30">
+        <v>1.523864959254948</v>
+      </c>
+      <c r="AQ30">
+        <v>2.397183098591549</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M&amp;G Credit Income Investment Trust plc (LSE:MGCI)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="J31">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="K31">
+        <v>18.5</v>
+      </c>
+      <c r="L31">
+        <v>0.8851674641148326</v>
+      </c>
+      <c r="M31">
+        <v>16.61</v>
+      </c>
+      <c r="N31">
+        <v>0.09448236632536973</v>
+      </c>
+      <c r="O31">
+        <v>0.8978378378378378</v>
+      </c>
+      <c r="P31">
+        <v>14.9</v>
+      </c>
+      <c r="Q31">
+        <v>0.08475540386803185</v>
+      </c>
+      <c r="R31">
+        <v>0.8054054054054054</v>
+      </c>
+      <c r="S31">
+        <v>1.709999999999999</v>
+      </c>
+      <c r="T31">
+        <v>0.1029500301023479</v>
+      </c>
+      <c r="U31">
+        <v>4.24</v>
+      </c>
+      <c r="V31">
+        <v>0.02411831626848692</v>
+      </c>
+      <c r="W31">
+        <v>0.1087595532039976</v>
+      </c>
+      <c r="X31">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y31">
+        <v>0.03674081930006808</v>
+      </c>
+      <c r="Z31">
+        <v>0.126222973789105</v>
+      </c>
+      <c r="AA31">
+        <v>0.1129363449691992</v>
+      </c>
+      <c r="AB31">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC31">
+        <v>0.04091761106526962</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>-4.24</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>-0.02471438563767778</v>
+      </c>
+      <c r="AK31">
+        <v>-0.02516917962721121</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Life Settlement Assets PLC (LSE:LSAA)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>-0.0134</v>
+      </c>
+      <c r="E32">
+        <v>-0.0673</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0.6347305389221557</v>
+      </c>
+      <c r="J32">
+        <v>0.6347305389221557</v>
+      </c>
+      <c r="K32">
+        <v>6.95</v>
+      </c>
+      <c r="L32">
+        <v>0.4161676646706587</v>
+      </c>
+      <c r="M32">
+        <v>2.94</v>
+      </c>
+      <c r="N32">
+        <v>0.03462897526501767</v>
+      </c>
+      <c r="O32">
+        <v>0.4230215827338129</v>
+      </c>
+      <c r="P32">
+        <v>-0</v>
+      </c>
+      <c r="Q32">
+        <v>-0</v>
+      </c>
+      <c r="R32">
+        <v>-0</v>
+      </c>
+      <c r="S32">
+        <v>2.94</v>
+      </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
+      <c r="U32">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="V32">
+        <v>0.1153121319199057</v>
+      </c>
+      <c r="W32">
+        <v>0.06447124304267161</v>
+      </c>
+      <c r="X32">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y32">
+        <v>-0.007547490861257958</v>
+      </c>
+      <c r="Z32">
+        <v>0.1778487752928647</v>
+      </c>
+      <c r="AA32">
+        <v>0.1128860489882854</v>
+      </c>
+      <c r="AB32">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC32">
+        <v>0.04086731508435584</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>-9.789999999999999</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>-0.1303421648249234</v>
+      </c>
+      <c r="AK32">
+        <v>-0.09887890112109889</v>
+      </c>
+      <c r="AL32">
+        <v>2.58</v>
+      </c>
+      <c r="AM32">
+        <v>2.58</v>
+      </c>
+      <c r="AO32">
+        <v>4.108527131782946</v>
+      </c>
+      <c r="AQ32">
+        <v>4.108527131782946</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Premier Miton Group plc (AIM:PMI)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0.0568</v>
+      </c>
+      <c r="E33">
+        <v>-0.298</v>
+      </c>
+      <c r="G33">
+        <v>0.1200466200466201</v>
+      </c>
+      <c r="H33">
+        <v>0.1200466200466201</v>
+      </c>
+      <c r="I33">
+        <v>0.03694638694638695</v>
+      </c>
+      <c r="J33">
+        <v>0.02195870167568281</v>
+      </c>
+      <c r="K33">
+        <v>2.53</v>
+      </c>
+      <c r="L33">
+        <v>0.02948717948717949</v>
+      </c>
+      <c r="M33">
+        <v>13.12</v>
+      </c>
+      <c r="N33">
+        <v>0.1093333333333333</v>
+      </c>
+      <c r="O33">
+        <v>5.185770750988143</v>
+      </c>
+      <c r="P33">
+        <v>12.1</v>
+      </c>
+      <c r="Q33">
+        <v>0.1008333333333333</v>
+      </c>
+      <c r="R33">
+        <v>4.782608695652174</v>
+      </c>
+      <c r="S33">
+        <v>1.02</v>
+      </c>
+      <c r="T33">
+        <v>0.07774390243902436</v>
+      </c>
+      <c r="U33">
+        <v>48.1</v>
+      </c>
+      <c r="V33">
+        <v>0.4008333333333333</v>
+      </c>
+      <c r="W33">
+        <v>0.01712931618144888</v>
+      </c>
+      <c r="X33">
+        <v>0.07252672187331821</v>
+      </c>
+      <c r="Y33">
+        <v>-0.05539740569186933</v>
+      </c>
+      <c r="Z33">
+        <v>4.693654266958424</v>
+      </c>
+      <c r="AA33">
+        <v>0.1030665538169357</v>
+      </c>
+      <c r="AB33">
+        <v>0.07185687862338405</v>
+      </c>
+      <c r="AC33">
+        <v>0.03120967519355165</v>
+      </c>
+      <c r="AD33">
+        <v>3.1</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>3.1</v>
+      </c>
+      <c r="AG33">
+        <v>-45</v>
+      </c>
+      <c r="AH33">
+        <v>0.02518277822908205</v>
+      </c>
+      <c r="AI33">
+        <v>0.01906519065190652</v>
+      </c>
+      <c r="AJ33">
+        <v>-0.6</v>
+      </c>
+      <c r="AK33">
+        <v>-0.3930131004366812</v>
+      </c>
+      <c r="AL33">
+        <v>0.015</v>
+      </c>
+      <c r="AM33">
+        <v>-1.075</v>
+      </c>
+      <c r="AN33">
+        <v>0.3009708737864077</v>
+      </c>
+      <c r="AO33">
+        <v>211.3333333333333</v>
+      </c>
+      <c r="AP33">
+        <v>-4.368932038834951</v>
+      </c>
+      <c r="AQ33">
+        <v>-2.948837209302325</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BioPharma Credit PLC (LSE:BPCR)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>-0.008020000000000001</v>
+      </c>
+      <c r="E34">
+        <v>-0.009849999999999999</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0.8020527859237536</v>
+      </c>
+      <c r="J34">
+        <v>0.8020527859237536</v>
+      </c>
+      <c r="K34">
+        <v>109.4</v>
+      </c>
+      <c r="L34">
+        <v>0.8020527859237536</v>
+      </c>
+      <c r="M34">
+        <v>210.2</v>
+      </c>
+      <c r="N34">
+        <v>0.199809885931559</v>
+      </c>
+      <c r="O34">
+        <v>1.921389396709324</v>
+      </c>
+      <c r="P34">
+        <v>130.8</v>
+      </c>
+      <c r="Q34">
+        <v>0.1243346007604563</v>
+      </c>
+      <c r="R34">
+        <v>1.195612431444241</v>
+      </c>
+      <c r="S34">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="T34">
+        <v>0.3777354900095147</v>
+      </c>
+      <c r="U34">
+        <v>37.1</v>
+      </c>
+      <c r="V34">
+        <v>0.03526615969581749</v>
+      </c>
+      <c r="W34">
+        <v>0.08238572181640183</v>
+      </c>
+      <c r="X34">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y34">
+        <v>0.01036698791247226</v>
+      </c>
+      <c r="Z34">
+        <v>0.1082539682539683</v>
+      </c>
+      <c r="AA34">
+        <v>0.08682539682539683</v>
+      </c>
+      <c r="AB34">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC34">
+        <v>0.01480666292146726</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>-37.1</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34">
+        <v>-0.03655532564784708</v>
+      </c>
+      <c r="AK34">
+        <v>-0.0311502938706969</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Petershill Partners plc (LSE:PHLL)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="F35">
+        <v>0.128</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0.9364091930188352</v>
+      </c>
+      <c r="J35">
+        <v>0.7476957350789726</v>
+      </c>
+      <c r="K35">
+        <v>344.7</v>
+      </c>
+      <c r="L35">
+        <v>0.5956454121306376</v>
+      </c>
+      <c r="M35">
+        <v>303.6</v>
+      </c>
+      <c r="N35">
+        <v>0.09039749888343011</v>
+      </c>
+      <c r="O35">
+        <v>0.8807658833768496</v>
+      </c>
+      <c r="P35">
+        <v>168.4</v>
+      </c>
+      <c r="Q35">
+        <v>0.05014143218698824</v>
+      </c>
+      <c r="R35">
+        <v>0.4885407600812301</v>
+      </c>
+      <c r="S35">
+        <v>135.2</v>
+      </c>
+      <c r="T35">
+        <v>0.4453227931488801</v>
+      </c>
+      <c r="U35">
+        <v>47.1</v>
+      </c>
+      <c r="V35">
+        <v>0.01402411790978115</v>
+      </c>
+      <c r="W35">
+        <v>0.0732889673208173</v>
+      </c>
+      <c r="X35">
+        <v>0.07491169424826447</v>
+      </c>
+      <c r="Y35">
+        <v>-0.001622726927447166</v>
+      </c>
+      <c r="Z35">
+        <v>0.1118974418469749</v>
+      </c>
+      <c r="AA35">
+        <v>0.08366524003523049</v>
+      </c>
+      <c r="AB35">
+        <v>0.07085777704732253</v>
+      </c>
+      <c r="AC35">
+        <v>0.01280746298790796</v>
+      </c>
+      <c r="AD35">
+        <v>494.1</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>494.1</v>
+      </c>
+      <c r="AG35">
+        <v>447</v>
+      </c>
+      <c r="AH35">
+        <v>0.1282510512381249</v>
+      </c>
+      <c r="AI35">
+        <v>0.09432269395235186</v>
+      </c>
+      <c r="AJ35">
+        <v>0.117461568782026</v>
+      </c>
+      <c r="AK35">
+        <v>0.08610559975343363</v>
+      </c>
+      <c r="AL35">
+        <v>34.1</v>
+      </c>
+      <c r="AM35">
+        <v>34.1</v>
+      </c>
+      <c r="AO35">
+        <v>15.89149560117302</v>
+      </c>
+      <c r="AQ35">
+        <v>15.89149560117302</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Literacy Capital plc (LSE:BOOK)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0.8567567567567568</v>
+      </c>
+      <c r="J36">
+        <v>0.8567567567567568</v>
+      </c>
+      <c r="K36">
+        <v>26.4</v>
+      </c>
+      <c r="L36">
+        <v>0.7135135135135134</v>
+      </c>
+      <c r="M36">
+        <v>-0</v>
+      </c>
+      <c r="N36">
+        <v>-0</v>
+      </c>
+      <c r="O36">
+        <v>-0</v>
+      </c>
+      <c r="P36">
+        <v>-0</v>
+      </c>
+      <c r="Q36">
+        <v>-0</v>
+      </c>
+      <c r="R36">
+        <v>-0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>1.78</v>
+      </c>
+      <c r="V36">
+        <v>0.005219941348973607</v>
+      </c>
+      <c r="W36">
+        <v>0.07072060005357621</v>
+      </c>
+      <c r="X36">
+        <v>0.07249332374270379</v>
+      </c>
+      <c r="Y36">
+        <v>-0.001772723689127578</v>
+      </c>
+      <c r="Z36">
+        <v>0.09379150908003205</v>
+      </c>
+      <c r="AA36">
+        <v>0.08035650913073016</v>
+      </c>
+      <c r="AB36">
+        <v>0.0718054080766586</v>
+      </c>
+      <c r="AC36">
+        <v>0.008551101054071558</v>
+      </c>
+      <c r="AD36">
+        <v>8.23</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>8.23</v>
+      </c>
+      <c r="AG36">
+        <v>6.45</v>
+      </c>
+      <c r="AH36">
+        <v>0.02356613120293216</v>
+      </c>
+      <c r="AI36">
+        <v>0.02027443155223807</v>
+      </c>
+      <c r="AJ36">
+        <v>0.01856382213268096</v>
+      </c>
+      <c r="AK36">
+        <v>0.01595942100705184</v>
+      </c>
+      <c r="AL36">
+        <v>1.85</v>
+      </c>
+      <c r="AM36">
+        <v>1.85</v>
+      </c>
+      <c r="AO36">
+        <v>17.13513513513513</v>
+      </c>
+      <c r="AQ36">
+        <v>17.13513513513513</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>RIT Capital Partners Plc (LSE:RCP)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>0.0784</v>
+      </c>
+      <c r="E37">
+        <v>0.0611</v>
+      </c>
+      <c r="G37">
+        <v>0.3201005025125628</v>
+      </c>
+      <c r="H37">
+        <v>0.3201005025125628</v>
+      </c>
+      <c r="I37">
+        <v>0.864104441397281</v>
+      </c>
+      <c r="J37">
+        <v>0.864104441397281</v>
+      </c>
+      <c r="K37">
+        <v>303.6</v>
+      </c>
+      <c r="L37">
+        <v>0.7628140703517589</v>
+      </c>
+      <c r="M37">
+        <v>202.1</v>
+      </c>
+      <c r="N37">
+        <v>0.0571388182075205</v>
+      </c>
+      <c r="O37">
+        <v>0.6656785243741766</v>
+      </c>
+      <c r="P37">
+        <v>71.2</v>
+      </c>
+      <c r="Q37">
+        <v>0.02013005371783998</v>
+      </c>
+      <c r="R37">
+        <v>0.2345191040843215</v>
+      </c>
+      <c r="S37">
+        <v>130.9</v>
+      </c>
+      <c r="T37">
+        <v>0.6476991588322614</v>
+      </c>
+      <c r="U37">
+        <v>182.4</v>
+      </c>
+      <c r="V37">
+        <v>0.05156912637828669</v>
+      </c>
+      <c r="W37">
+        <v>0.06727977839335181</v>
+      </c>
+      <c r="X37">
+        <v>0.07401839694156519</v>
+      </c>
+      <c r="Y37">
+        <v>-0.006738618548213379</v>
+      </c>
+      <c r="Z37">
+        <v>0.08495955162464598</v>
+      </c>
+      <c r="AA37">
+        <v>0.07341392589797818</v>
+      </c>
+      <c r="AB37">
+        <v>0.07118317116769153</v>
+      </c>
+      <c r="AC37">
+        <v>0.002230754730286652</v>
+      </c>
+      <c r="AD37">
+        <v>359.2</v>
+      </c>
+      <c r="AE37">
+        <v>0.4821616194106979</v>
+      </c>
+      <c r="AF37">
+        <v>359.6821616194107</v>
+      </c>
+      <c r="AG37">
+        <v>177.2821616194107</v>
+      </c>
+      <c r="AH37">
+        <v>0.09230472147872883</v>
+      </c>
+      <c r="AI37">
+        <v>0.07250220821233508</v>
+      </c>
+      <c r="AJ37">
+        <v>0.04772985839668047</v>
+      </c>
+      <c r="AK37">
+        <v>0.03709932269100751</v>
+      </c>
+      <c r="AL37">
+        <v>40.4</v>
+      </c>
+      <c r="AM37">
+        <v>40.4</v>
+      </c>
+      <c r="AN37">
+        <v>1.043245912114083</v>
+      </c>
+      <c r="AO37">
+        <v>8.502475247524753</v>
+      </c>
+      <c r="AP37">
+        <v>0.514891120267813</v>
+      </c>
+      <c r="AQ37">
+        <v>8.502475247524753</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Frenkel Topping Group Plc (AIM:FEN)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>0.337</v>
+      </c>
+      <c r="E38">
+        <v>0.0191</v>
+      </c>
+      <c r="F38">
+        <v>0.065</v>
+      </c>
+      <c r="G38">
+        <v>0.1538812785388128</v>
+      </c>
+      <c r="H38">
+        <v>0.1538812785388128</v>
+      </c>
+      <c r="I38">
+        <v>0.1308219178082192</v>
+      </c>
+      <c r="J38">
+        <v>0.06891880212609655</v>
+      </c>
+      <c r="K38">
+        <v>1.33</v>
+      </c>
+      <c r="L38">
+        <v>0.03036529680365297</v>
+      </c>
+      <c r="M38">
+        <v>1.84</v>
+      </c>
+      <c r="N38">
+        <v>0.02813455657492355</v>
+      </c>
+      <c r="O38">
+        <v>1.383458646616541</v>
+      </c>
+      <c r="P38">
+        <v>1.84</v>
+      </c>
+      <c r="Q38">
+        <v>0.02813455657492355</v>
+      </c>
+      <c r="R38">
+        <v>1.383458646616541</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>5.21</v>
+      </c>
+      <c r="V38">
+        <v>0.07966360856269113</v>
+      </c>
+      <c r="W38">
+        <v>0.02577519379844961</v>
+      </c>
+      <c r="X38">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y38">
+        <v>-0.04624354010547996</v>
+      </c>
+      <c r="Z38">
+        <v>0.9609477841158403</v>
+      </c>
+      <c r="AA38">
+        <v>0.06622737018699054</v>
+      </c>
+      <c r="AB38">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC38">
+        <v>-0.00579136371693903</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>-5.21</v>
+      </c>
+      <c r="AH38">
+        <v>0</v>
+      </c>
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38">
+        <v>-0.08655922910782521</v>
+      </c>
+      <c r="AK38">
+        <v>-0.1076668733209341</v>
+      </c>
+      <c r="AL38">
+        <v>0.265</v>
+      </c>
+      <c r="AM38">
+        <v>0.249</v>
+      </c>
+      <c r="AN38">
+        <v>0</v>
+      </c>
+      <c r="AO38">
+        <v>21.62264150943396</v>
+      </c>
+      <c r="AP38">
+        <v>-0.8513071895424836</v>
+      </c>
+      <c r="AQ38">
+        <v>23.01204819277109</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Aquila Energy Efficiency Trust Plc (LSE:AEET)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0.5857307249712314</v>
+      </c>
+      <c r="J39">
+        <v>0.5857307249712314</v>
+      </c>
+      <c r="K39">
+        <v>1.97</v>
+      </c>
+      <c r="L39">
+        <v>0.2266973532796318</v>
+      </c>
+      <c r="M39">
+        <v>6.2678</v>
+      </c>
+      <c r="N39">
+        <v>0.1182603773584906</v>
+      </c>
+      <c r="O39">
+        <v>3.181624365482234</v>
+      </c>
+      <c r="P39">
+        <v>6.2678</v>
+      </c>
+      <c r="Q39">
+        <v>0.1182603773584906</v>
+      </c>
+      <c r="R39">
+        <v>3.181624365482234</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>17.3</v>
+      </c>
+      <c r="V39">
+        <v>0.3264150943396227</v>
+      </c>
+      <c r="W39">
+        <v>0.01656854499579478</v>
+      </c>
+      <c r="X39">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y39">
+        <v>-0.05545018890813479</v>
+      </c>
+      <c r="Z39">
+        <v>0.1049757794663026</v>
+      </c>
+      <c r="AA39">
+        <v>0.06148753941121755</v>
+      </c>
+      <c r="AB39">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC39">
+        <v>-0.01053119449271202</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>-17.3</v>
+      </c>
+      <c r="AH39">
+        <v>0</v>
+      </c>
+      <c r="AI39">
+        <v>0</v>
+      </c>
+      <c r="AJ39">
+        <v>-0.484593837535014</v>
+      </c>
+      <c r="AK39">
+        <v>-0.2146401985111663</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>VH Global Energy Infrastructure PLC (LSE:ENRG)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0.7400611620795107</v>
+      </c>
+      <c r="J40">
+        <v>0.7400611620795107</v>
+      </c>
+      <c r="K40">
+        <v>24.2</v>
+      </c>
+      <c r="L40">
+        <v>0.7400611620795107</v>
+      </c>
+      <c r="M40">
+        <v>46.9</v>
+      </c>
+      <c r="N40">
+        <v>0.1434250764525994</v>
+      </c>
+      <c r="O40">
+        <v>1.93801652892562</v>
+      </c>
+      <c r="P40">
+        <v>29.4</v>
+      </c>
+      <c r="Q40">
+        <v>0.08990825688073394</v>
+      </c>
+      <c r="R40">
+        <v>1.214876033057851</v>
+      </c>
+      <c r="S40">
+        <v>17.5</v>
+      </c>
+      <c r="T40">
+        <v>0.373134328358209</v>
+      </c>
+      <c r="U40">
+        <v>95.8</v>
+      </c>
+      <c r="V40">
+        <v>0.2929663608562691</v>
+      </c>
+      <c r="W40">
+        <v>0.04089910427581545</v>
+      </c>
+      <c r="X40">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y40">
+        <v>-0.03111962962811413</v>
+      </c>
+      <c r="Z40">
+        <v>0.07808022922636103</v>
+      </c>
+      <c r="AA40">
+        <v>0.05778414517669531</v>
+      </c>
+      <c r="AB40">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC40">
+        <v>-0.01423458872723427</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>-95.8</v>
+      </c>
+      <c r="AH40">
+        <v>0</v>
+      </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AJ40">
+        <v>-0.4143598615916955</v>
+      </c>
+      <c r="AK40">
+        <v>-0.2038297872340426</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Caledonia Investments Plc (LSE:CLDN)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>-0.0194</v>
+      </c>
+      <c r="E41">
+        <v>-0.0165</v>
+      </c>
+      <c r="G41">
+        <v>1.469170403587444</v>
+      </c>
+      <c r="H41">
+        <v>1.469170403587444</v>
+      </c>
+      <c r="I41">
+        <v>0.7713004484304932</v>
+      </c>
+      <c r="J41">
+        <v>0.7713004484304932</v>
+      </c>
+      <c r="K41">
+        <v>143.8</v>
+      </c>
+      <c r="L41">
+        <v>0.8060538116591929</v>
+      </c>
+      <c r="M41">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="N41">
+        <v>0.03967033905542745</v>
+      </c>
+      <c r="O41">
+        <v>0.6460361613351877</v>
+      </c>
+      <c r="P41">
+        <v>51.2</v>
+      </c>
+      <c r="Q41">
+        <v>0.02186352378512256</v>
+      </c>
+      <c r="R41">
+        <v>0.3560500695410292</v>
+      </c>
+      <c r="S41">
+        <v>41.7</v>
+      </c>
+      <c r="T41">
+        <v>0.4488697524219591</v>
+      </c>
+      <c r="U41">
+        <v>180.4</v>
+      </c>
+      <c r="V41">
+        <v>0.07703475958664276</v>
+      </c>
+      <c r="W41">
+        <v>0.04097099549831899</v>
+      </c>
+      <c r="X41">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y41">
+        <v>-0.03104773840561058</v>
+      </c>
+      <c r="Z41">
+        <v>0.04963276207433785</v>
+      </c>
+      <c r="AA41">
+        <v>0.03828177164478076</v>
+      </c>
+      <c r="AB41">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC41">
+        <v>-0.03373696225914881</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>-180.4</v>
+      </c>
+      <c r="AH41">
+        <v>0</v>
+      </c>
+      <c r="AI41">
+        <v>0</v>
+      </c>
+      <c r="AJ41">
+        <v>-0.08346442120847598</v>
+      </c>
+      <c r="AK41">
+        <v>-0.04836201812235269</v>
+      </c>
+      <c r="AL41">
+        <v>6.7</v>
+      </c>
+      <c r="AM41">
+        <v>-2.819999999999999</v>
+      </c>
+      <c r="AN41">
+        <v>0</v>
+      </c>
+      <c r="AO41">
+        <v>20.53731343283582</v>
+      </c>
+      <c r="AP41">
+        <v>-1.296908698777858</v>
+      </c>
+      <c r="AQ41">
+        <v>-48.79432624113476</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Manolete Partners Plc (AIM:MANO)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>0.148</v>
+      </c>
+      <c r="E42">
+        <v>-0.5629999999999999</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0.05417721518987342</v>
+      </c>
+      <c r="J42">
+        <v>0.05417721518987342</v>
+      </c>
+      <c r="K42">
+        <v>0.121</v>
+      </c>
+      <c r="L42">
+        <v>0.003063291139240506</v>
+      </c>
+      <c r="M42">
+        <v>-0</v>
+      </c>
+      <c r="N42">
+        <v>-0</v>
+      </c>
+      <c r="O42">
+        <v>-0</v>
+      </c>
+      <c r="P42">
+        <v>-0</v>
+      </c>
+      <c r="Q42">
+        <v>-0</v>
+      </c>
+      <c r="R42">
+        <v>-0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0.852</v>
+      </c>
+      <c r="V42">
+        <v>0.01786163522012579</v>
+      </c>
+      <c r="W42">
+        <v>0.002489711934156378</v>
+      </c>
+      <c r="X42">
+        <v>0.0789444371993072</v>
+      </c>
+      <c r="Y42">
+        <v>-0.07645472526515082</v>
+      </c>
+      <c r="Z42">
+        <v>0.6246046805819101</v>
+      </c>
+      <c r="AA42">
+        <v>0.0338393421884883</v>
+      </c>
+      <c r="AB42">
+        <v>0.070833039137285</v>
+      </c>
+      <c r="AC42">
+        <v>-0.03699369694879671</v>
+      </c>
+      <c r="AD42">
+        <v>16.8</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>16.8</v>
+      </c>
+      <c r="AG42">
+        <v>15.948</v>
+      </c>
+      <c r="AH42">
+        <v>0.2604651162790698</v>
+      </c>
+      <c r="AI42">
+        <v>0.2362869198312237</v>
+      </c>
+      <c r="AJ42">
+        <v>0.2505656108597285</v>
+      </c>
+      <c r="AK42">
+        <v>0.2270242569183465</v>
+      </c>
+      <c r="AL42">
+        <v>0.265</v>
+      </c>
+      <c r="AM42">
+        <v>0.231</v>
+      </c>
+      <c r="AO42">
+        <v>8.075471698113208</v>
+      </c>
+      <c r="AQ42">
+        <v>9.264069264069263</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HICL Infrastructure PLC (LSE:HICL)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>-0.09570000000000001</v>
+      </c>
+      <c r="E43">
+        <v>-0.0974</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0.9630662020905922</v>
+      </c>
+      <c r="J43">
+        <v>0.9630662020905922</v>
+      </c>
+      <c r="K43">
+        <v>138.2</v>
+      </c>
+      <c r="L43">
+        <v>0.9630662020905922</v>
+      </c>
+      <c r="M43">
+        <v>248.1</v>
+      </c>
+      <c r="N43">
+        <v>0.08329416504398039</v>
+      </c>
+      <c r="O43">
+        <v>1.795224312590449</v>
+      </c>
+      <c r="P43">
+        <v>224.4</v>
+      </c>
+      <c r="Q43">
+        <v>0.07533740683542604</v>
+      </c>
+      <c r="R43">
+        <v>1.623733719247468</v>
+      </c>
+      <c r="S43">
+        <v>23.69999999999999</v>
+      </c>
+      <c r="T43">
+        <v>0.09552599758162027</v>
+      </c>
+      <c r="U43">
+        <v>3.08</v>
+      </c>
+      <c r="V43">
+        <v>0.001034042838917612</v>
+      </c>
+      <c r="W43">
+        <v>0.03496963562753036</v>
+      </c>
+      <c r="X43">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y43">
+        <v>-0.03704909827639921</v>
+      </c>
+      <c r="Z43">
+        <v>0.03632083829000987</v>
+      </c>
+      <c r="AA43">
+        <v>0.03497937178870637</v>
+      </c>
+      <c r="AB43">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC43">
+        <v>-0.03703936211522321</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>-3.08</v>
+      </c>
+      <c r="AH43">
+        <v>0</v>
+      </c>
+      <c r="AI43">
+        <v>0</v>
+      </c>
+      <c r="AJ43">
+        <v>-0.001035113190299511</v>
+      </c>
+      <c r="AK43">
+        <v>-0.0007285250678852904</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HydrogenOne Capital Growth plc (LSE:HGEN)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0.6794520547945205</v>
+      </c>
+      <c r="J44">
+        <v>0.6794520547945205</v>
+      </c>
+      <c r="K44">
+        <v>4.73</v>
+      </c>
+      <c r="L44">
+        <v>0.6479452054794521</v>
+      </c>
+      <c r="M44">
+        <v>-0</v>
+      </c>
+      <c r="N44">
+        <v>-0</v>
+      </c>
+      <c r="O44">
+        <v>-0</v>
+      </c>
+      <c r="P44">
+        <v>-0</v>
+      </c>
+      <c r="Q44">
+        <v>-0</v>
+      </c>
+      <c r="R44">
+        <v>-0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>2.08</v>
+      </c>
+      <c r="V44">
+        <v>0.05959885386819485</v>
+      </c>
+      <c r="W44">
+        <v>0.02870145631067961</v>
+      </c>
+      <c r="X44">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y44">
+        <v>-0.04331727759324996</v>
+      </c>
+      <c r="Z44">
+        <v>0.04743339831059129</v>
+      </c>
+      <c r="AA44">
+        <v>0.03222871994801819</v>
+      </c>
+      <c r="AB44">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC44">
+        <v>-0.03979001395591138</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>-2.08</v>
+      </c>
+      <c r="AH44">
+        <v>0</v>
+      </c>
+      <c r="AI44">
+        <v>0</v>
+      </c>
+      <c r="AJ44">
+        <v>-0.06337599024984765</v>
+      </c>
+      <c r="AK44">
+        <v>-0.01248349537870604</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>RM Infrastructure Income PLC (LSE:RMII)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>-0.0517</v>
+      </c>
+      <c r="E45">
+        <v>-0.156</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0.448692152917505</v>
+      </c>
+      <c r="J45">
+        <v>0.448692152917505</v>
+      </c>
+      <c r="K45">
+        <v>3.95</v>
+      </c>
+      <c r="L45">
+        <v>0.3973843058350101</v>
+      </c>
+      <c r="M45">
+        <v>9.66</v>
+      </c>
+      <c r="N45">
+        <v>0.1075723830734967</v>
+      </c>
+      <c r="O45">
+        <v>2.445569620253164</v>
+      </c>
+      <c r="P45">
+        <v>9.66</v>
+      </c>
+      <c r="Q45">
+        <v>0.1075723830734967</v>
+      </c>
+      <c r="R45">
+        <v>2.445569620253164</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>20.1</v>
+      </c>
+      <c r="V45">
+        <v>0.2238307349665924</v>
+      </c>
+      <c r="W45">
+        <v>0.02961019490254873</v>
+      </c>
+      <c r="X45">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y45">
+        <v>-0.04240853900138085</v>
+      </c>
+      <c r="Z45">
+        <v>0.06643940913040572</v>
+      </c>
+      <c r="AA45">
+        <v>0.02981084152128868</v>
+      </c>
+      <c r="AB45">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC45">
+        <v>-0.04220789238264089</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>-20.1</v>
+      </c>
+      <c r="AH45">
+        <v>0</v>
+      </c>
+      <c r="AI45">
+        <v>0</v>
+      </c>
+      <c r="AJ45">
+        <v>-0.2883787661406026</v>
+      </c>
+      <c r="AK45">
+        <v>-0.1820652173913044</v>
+      </c>
+      <c r="AL45">
+        <v>0.514</v>
+      </c>
+      <c r="AM45">
+        <v>0.514</v>
+      </c>
+      <c r="AO45">
+        <v>8.67704280155642</v>
+      </c>
+      <c r="AQ45">
+        <v>8.67704280155642</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Octopus Renewables Infrastructure Trust plc (LSE:ORIT)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0.71875</v>
+      </c>
+      <c r="J46">
+        <v>0.71875</v>
+      </c>
+      <c r="K46">
+        <v>23.3</v>
+      </c>
+      <c r="L46">
+        <v>0.728125</v>
+      </c>
+      <c r="M46">
+        <v>42.91999999999999</v>
+      </c>
+      <c r="N46">
+        <v>0.09033887602609975</v>
+      </c>
+      <c r="O46">
+        <v>1.84206008583691</v>
+      </c>
+      <c r="P46">
+        <v>41.8</v>
+      </c>
+      <c r="Q46">
+        <v>0.08798147758366659</v>
+      </c>
+      <c r="R46">
+        <v>1.793991416309013</v>
+      </c>
+      <c r="S46">
+        <v>1.119999999999997</v>
+      </c>
+      <c r="T46">
+        <v>0.02609506057781914</v>
+      </c>
+      <c r="U46">
+        <v>14.9</v>
+      </c>
+      <c r="V46">
+        <v>0.03136181856451273</v>
+      </c>
+      <c r="W46">
+        <v>0.03014230271668823</v>
+      </c>
+      <c r="X46">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y46">
+        <v>-0.04187643118724134</v>
+      </c>
+      <c r="Z46">
+        <v>0.04141633512027562</v>
+      </c>
+      <c r="AA46">
+        <v>0.02976799086769811</v>
+      </c>
+      <c r="AB46">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC46">
+        <v>-0.04225074303623147</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>-14.9</v>
+      </c>
+      <c r="AH46">
+        <v>0</v>
+      </c>
+      <c r="AI46">
+        <v>0</v>
+      </c>
+      <c r="AJ46">
+        <v>-0.03237722729248153</v>
+      </c>
+      <c r="AK46">
+        <v>-0.02029143401879341</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>-0.307</v>
+      </c>
+      <c r="AQ46">
+        <v>-74.9185667752443</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>abrdn plc (LSE:ABDN)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>-0.124</v>
+      </c>
+      <c r="E47">
+        <v>-0.247</v>
+      </c>
+      <c r="F47">
+        <v>-0.0209</v>
+      </c>
+      <c r="G47">
+        <v>0.2033044846577498</v>
+      </c>
+      <c r="H47">
+        <v>0.2004608294930876</v>
+      </c>
+      <c r="I47">
+        <v>0.06603349443632685</v>
+      </c>
+      <c r="J47">
+        <v>0.06188307357869654</v>
+      </c>
+      <c r="K47">
+        <v>400.6</v>
+      </c>
+      <c r="L47">
+        <v>0.2251320669888726</v>
+      </c>
+      <c r="M47">
+        <v>616.7</v>
+      </c>
+      <c r="N47">
+        <v>0.1955728918910348</v>
+      </c>
+      <c r="O47">
+        <v>1.539440838741887</v>
+      </c>
+      <c r="P47">
+        <v>337.4</v>
+      </c>
+      <c r="Q47">
+        <v>0.1069990169029271</v>
+      </c>
+      <c r="R47">
+        <v>0.8422366450324512</v>
+      </c>
+      <c r="S47">
+        <v>279.3000000000001</v>
+      </c>
+      <c r="T47">
+        <v>0.4528944381384791</v>
+      </c>
+      <c r="U47">
+        <v>1765.5</v>
+      </c>
+      <c r="V47">
+        <v>0.5598896394253638</v>
+      </c>
+      <c r="W47">
+        <v>0.0587907249779865</v>
+      </c>
+      <c r="X47">
+        <v>0.07677869004246765</v>
+      </c>
+      <c r="Y47">
+        <v>-0.01798796506448115</v>
+      </c>
+      <c r="Z47">
+        <v>0.3841537132987911</v>
+      </c>
+      <c r="AA47">
+        <v>0.02377261250559858</v>
+      </c>
+      <c r="AB47">
+        <v>0.07092692588847405</v>
+      </c>
+      <c r="AC47">
+        <v>-0.04715431338287547</v>
+      </c>
+      <c r="AD47">
+        <v>763.3</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>763.3</v>
+      </c>
+      <c r="AG47">
+        <v>-1002.2</v>
+      </c>
+      <c r="AH47">
+        <v>0.1948884236327427</v>
+      </c>
+      <c r="AI47">
+        <v>0.1050943136444995</v>
+      </c>
+      <c r="AJ47">
+        <v>-0.46590116684487</v>
+      </c>
+      <c r="AK47">
+        <v>-0.1823010459299682</v>
+      </c>
+      <c r="AL47">
+        <v>31.6</v>
+      </c>
+      <c r="AM47">
+        <v>-61.9</v>
+      </c>
+      <c r="AN47">
+        <v>2.783734500364697</v>
+      </c>
+      <c r="AO47">
+        <v>3.718354430379747</v>
+      </c>
+      <c r="AP47">
+        <v>-3.654996353026988</v>
+      </c>
+      <c r="AQ47">
+        <v>-1.898222940226171</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Mercia Asset Management PLC (AIM:MERC)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>0.249</v>
+      </c>
+      <c r="G48">
+        <v>0.1174887892376682</v>
+      </c>
+      <c r="H48">
+        <v>0.1174887892376682</v>
+      </c>
+      <c r="I48">
+        <v>0.05896860986547085</v>
+      </c>
+      <c r="J48">
+        <v>0.05896860986547085</v>
+      </c>
+      <c r="K48">
+        <v>-9.59</v>
+      </c>
+      <c r="L48">
+        <v>-0.2150224215246637</v>
+      </c>
+      <c r="M48">
+        <v>12</v>
+      </c>
+      <c r="N48">
+        <v>0.07797270955165692</v>
+      </c>
+      <c r="O48">
+        <v>-1.251303441084463</v>
+      </c>
+      <c r="P48">
+        <v>5.26</v>
+      </c>
+      <c r="Q48">
+        <v>0.03417803768680961</v>
+      </c>
+      <c r="R48">
+        <v>-0.5484880083420229</v>
+      </c>
+      <c r="S48">
+        <v>6.74</v>
+      </c>
+      <c r="T48">
+        <v>0.5616666666666666</v>
+      </c>
+      <c r="U48">
+        <v>61.9</v>
+      </c>
+      <c r="V48">
+        <v>0.4022092267706303</v>
+      </c>
+      <c r="W48">
+        <v>-0.03882591093117409</v>
+      </c>
+      <c r="X48">
+        <v>0.07216439353672918</v>
+      </c>
+      <c r="Y48">
+        <v>-0.1109903044679033</v>
+      </c>
+      <c r="Z48">
+        <v>0.250056066382597</v>
+      </c>
+      <c r="AA48">
+        <v>0.01474545862300964</v>
+      </c>
+      <c r="AB48">
+        <v>0.07195217345555398</v>
+      </c>
+      <c r="AC48">
+        <v>-0.05720671483254434</v>
+      </c>
+      <c r="AD48">
+        <v>1.14</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>1.14</v>
+      </c>
+      <c r="AG48">
+        <v>-60.76</v>
+      </c>
+      <c r="AH48">
+        <v>0.007352941176470588</v>
+      </c>
+      <c r="AI48">
+        <v>0.004519505233111323</v>
+      </c>
+      <c r="AJ48">
+        <v>-0.6523512991196048</v>
+      </c>
+      <c r="AK48">
+        <v>-0.3192182410423453</v>
+      </c>
+      <c r="AL48">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AM48">
+        <v>-3.45</v>
+      </c>
+      <c r="AN48">
+        <v>0.168141592920354</v>
+      </c>
+      <c r="AO48">
+        <v>37.57142857142857</v>
+      </c>
+      <c r="AP48">
+        <v>-8.961651917404129</v>
+      </c>
+      <c r="AQ48">
+        <v>-0.7623188405797101</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Schroder BSC Social Impact Trust plc (LSE:SBSI)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0.4734982332155477</v>
+      </c>
+      <c r="J49">
+        <v>0.4734982332155477</v>
+      </c>
+      <c r="K49">
+        <v>1.33</v>
+      </c>
+      <c r="L49">
+        <v>0.4699646643109541</v>
+      </c>
+      <c r="M49">
+        <v>4.19</v>
+      </c>
+      <c r="N49">
+        <v>0.05310519645120405</v>
+      </c>
+      <c r="O49">
+        <v>3.150375939849623</v>
+      </c>
+      <c r="P49">
+        <v>2.44</v>
+      </c>
+      <c r="Q49">
+        <v>0.03092522179974651</v>
+      </c>
+      <c r="R49">
+        <v>1.834586466165413</v>
+      </c>
+      <c r="S49">
+        <v>1.75</v>
+      </c>
+      <c r="T49">
+        <v>0.4176610978520286</v>
+      </c>
+      <c r="U49">
+        <v>0.65</v>
+      </c>
+      <c r="V49">
+        <v>0.008238276299112801</v>
+      </c>
+      <c r="W49">
+        <v>0.01179078014184397</v>
+      </c>
+      <c r="X49">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y49">
+        <v>-0.0602279537620856</v>
+      </c>
+      <c r="Z49">
+        <v>0.02519474738482083</v>
+      </c>
+      <c r="AA49">
+        <v>0.01192966837302471</v>
+      </c>
+      <c r="AB49">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC49">
+        <v>-0.06008906553090487</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>-0.65</v>
+      </c>
+      <c r="AH49">
+        <v>0</v>
+      </c>
+      <c r="AI49">
+        <v>0</v>
+      </c>
+      <c r="AJ49">
+        <v>-0.008306709265175719</v>
+      </c>
+      <c r="AK49">
+        <v>-0.005982512655315233</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>Intermediate Capital Group plc (LSE:ICG)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="D50">
         <v>0.132</v>
       </c>
-      <c r="E6">
+      <c r="E50">
         <v>0.149</v>
       </c>
-      <c r="F6">
+      <c r="F50">
         <v>-0.00893</v>
       </c>
-      <c r="G6">
+      <c r="G50">
         <v>0.000117564484997368</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
         <v>537.3</v>
       </c>
-      <c r="L6">
+      <c r="L50">
         <v>0.4713984909633269</v>
       </c>
-      <c r="M6">
+      <c r="M50">
         <v>304.5</v>
       </c>
-      <c r="N6">
+      <c r="N50">
         <v>0.04050764257492916</v>
       </c>
-      <c r="O6">
+      <c r="O50">
         <v>0.5667225013958683</v>
       </c>
-      <c r="P6">
+      <c r="P50">
         <v>304.5</v>
       </c>
-      <c r="Q6">
+      <c r="Q50">
         <v>0.04050764257492916</v>
       </c>
-      <c r="R6">
+      <c r="R50">
         <v>0.5667225013958683</v>
       </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
         <v>1046.1</v>
       </c>
-      <c r="V6">
+      <c r="V50">
         <v>0.1391627090234266</v>
       </c>
-      <c r="W6">
+      <c r="W50">
         <v>0.2086601941747573</v>
       </c>
-      <c r="X6">
-        <v>0.07673056678604434</v>
-      </c>
-      <c r="Y6">
-        <v>0.1319296273887129</v>
-      </c>
-      <c r="Z6">
+      <c r="X50">
+        <v>0.07671612190641255</v>
+      </c>
+      <c r="Y50">
+        <v>0.1319440722683447</v>
+      </c>
+      <c r="Z50">
         <v>0.3103776924543202</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.07095016971190815</v>
-      </c>
-      <c r="AC6">
-        <v>-0.07095016971190815</v>
-      </c>
-      <c r="AD6">
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0.07093851010312453</v>
+      </c>
+      <c r="AC50">
+        <v>-0.07093851010312453</v>
+      </c>
+      <c r="AD50">
         <v>1795.7</v>
       </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
         <v>1795.7</v>
       </c>
-      <c r="AG6">
+      <c r="AG50">
         <v>749.6000000000001</v>
       </c>
-      <c r="AH6">
+      <c r="AH50">
         <v>0.1928206339661541</v>
       </c>
-      <c r="AI6">
+      <c r="AI50">
         <v>0.3704001650165016</v>
       </c>
-      <c r="AJ6">
+      <c r="AJ50">
         <v>0.09067705372155759</v>
       </c>
-      <c r="AK6">
+      <c r="AK50">
         <v>0.1971645756069334</v>
       </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>WH Ireland Group plc (AIM:WHI)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K51">
+        <v>-4.38</v>
+      </c>
+      <c r="M51">
+        <v>-0</v>
+      </c>
+      <c r="N51">
+        <v>-0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>-0</v>
+      </c>
+      <c r="Q51">
+        <v>-0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>6.16</v>
+      </c>
+      <c r="V51">
+        <v>0.7680798004987531</v>
+      </c>
+      <c r="W51">
+        <v>-0.2317460317460318</v>
+      </c>
+      <c r="X51">
+        <v>0.07276410439396648</v>
+      </c>
+      <c r="Y51">
+        <v>-0.3045101361399982</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0.07185248268124328</v>
+      </c>
+      <c r="AC51">
+        <v>-0.07185248268124328</v>
+      </c>
+      <c r="AD51">
+        <v>0.304</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0.304</v>
+      </c>
+      <c r="AG51">
+        <v>-5.856</v>
+      </c>
+      <c r="AH51">
+        <v>0.03652090341182124</v>
+      </c>
+      <c r="AI51">
+        <v>0.01669962645572402</v>
+      </c>
+      <c r="AJ51">
+        <v>-2.706099815157117</v>
+      </c>
+      <c r="AK51">
+        <v>-0.4862172035868483</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>-0.004</v>
+      </c>
+      <c r="AQ51">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>DT Cloud Acquisition Corporation (NasdaqGM:DYCQ)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K52">
+        <v>1.55</v>
+      </c>
+      <c r="M52">
+        <v>-0</v>
+      </c>
+      <c r="N52">
+        <v>-0</v>
+      </c>
+      <c r="O52">
+        <v>-0</v>
+      </c>
+      <c r="P52">
+        <v>-0</v>
+      </c>
+      <c r="Q52">
+        <v>-0</v>
+      </c>
+      <c r="R52">
+        <v>-0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0.168</v>
+      </c>
+      <c r="V52">
+        <v>0.001794871794871795</v>
+      </c>
+      <c r="W52">
+        <v>-25</v>
+      </c>
+      <c r="X52">
+        <v>0.07203343992454878</v>
+      </c>
+      <c r="Y52">
+        <v>-25.07203343992455</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0.07201533200931513</v>
+      </c>
+      <c r="AC52">
+        <v>-0.07201533200931513</v>
+      </c>
+      <c r="AD52">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AG52">
+        <v>-0.098</v>
+      </c>
+      <c r="AH52">
+        <v>0.0007473043663926552</v>
+      </c>
+      <c r="AI52">
+        <v>-0.04402515723270441</v>
+      </c>
+      <c r="AJ52">
+        <v>-0.00104810592286796</v>
+      </c>
+      <c r="AK52">
+        <v>0.05574516496018202</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>-2.17</v>
+      </c>
+      <c r="AQ52">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Logistics Development Group plc (AIM:LDG)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K53">
+        <v>-10.2</v>
+      </c>
+      <c r="M53">
+        <v>4.97</v>
+      </c>
+      <c r="N53">
+        <v>0.05826494724501759</v>
+      </c>
+      <c r="O53">
+        <v>-0.4872549019607843</v>
+      </c>
+      <c r="P53">
+        <v>-0</v>
+      </c>
+      <c r="Q53">
+        <v>-0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>4.97</v>
+      </c>
+      <c r="T53">
+        <v>1</v>
+      </c>
+      <c r="U53">
+        <v>40.6</v>
+      </c>
+      <c r="V53">
+        <v>0.4759671746776085</v>
+      </c>
+      <c r="W53">
+        <v>-0.074235807860262</v>
+      </c>
+      <c r="X53">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y53">
+        <v>-0.1462545417641916</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>-0.01591220850480109</v>
+      </c>
+      <c r="AB53">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC53">
+        <v>-0.08793094240873067</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>-40.6</v>
+      </c>
+      <c r="AH53">
+        <v>0</v>
+      </c>
+      <c r="AI53">
+        <v>0</v>
+      </c>
+      <c r="AJ53">
+        <v>-0.9082774049217004</v>
+      </c>
+      <c r="AK53">
+        <v>-0.4754098360655737</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>-1.97</v>
+      </c>
+      <c r="AQ53">
+        <v>0.5888324873096447</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Pantheon Infrastructure PLC (LSE:PINT)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K54">
+        <v>97.8</v>
+      </c>
+      <c r="M54">
+        <v>33.53</v>
+      </c>
+      <c r="N54">
+        <v>0.06407414484999045</v>
+      </c>
+      <c r="O54">
+        <v>0.3428425357873211</v>
+      </c>
+      <c r="P54">
+        <v>23.9</v>
+      </c>
+      <c r="Q54">
+        <v>0.04567169883432066</v>
+      </c>
+      <c r="R54">
+        <v>0.2443762781186094</v>
+      </c>
+      <c r="S54">
+        <v>9.630000000000003</v>
+      </c>
+      <c r="T54">
+        <v>0.2872054876230242</v>
+      </c>
+      <c r="U54">
+        <v>14</v>
+      </c>
+      <c r="V54">
+        <v>0.02675329638830499</v>
+      </c>
+      <c r="W54">
+        <v>0.1591020009760859</v>
+      </c>
+      <c r="X54">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y54">
+        <v>0.0870832670721563</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>-0.01697311436010415</v>
+      </c>
+      <c r="AB54">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC54">
+        <v>-0.08899184826403372</v>
+      </c>
+      <c r="AD54">
+        <v>0</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>-14</v>
+      </c>
+      <c r="AH54">
+        <v>0</v>
+      </c>
+      <c r="AI54">
+        <v>0</v>
+      </c>
+      <c r="AJ54">
+        <v>-0.02748870999410957</v>
+      </c>
+      <c r="AK54">
+        <v>-0.02116082224909311</v>
+      </c>
+      <c r="AL54">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="AM54">
+        <v>-28.064</v>
+      </c>
+      <c r="AO54">
+        <v>-9.252136752136751</v>
+      </c>
+      <c r="AQ54">
+        <v>0.3085803876852908</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tanfield Group PLC (AIM:TAN)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K55">
+        <v>-0.346</v>
+      </c>
+      <c r="M55">
+        <v>-0</v>
+      </c>
+      <c r="N55">
+        <v>-0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>-0</v>
+      </c>
+      <c r="Q55">
+        <v>-0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>4.21</v>
+      </c>
+      <c r="V55">
+        <v>0.5689189189189189</v>
+      </c>
+      <c r="W55">
+        <v>-0.01197231833910035</v>
+      </c>
+      <c r="X55">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y55">
+        <v>-0.08399105224302991</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>-0.02250618301731245</v>
+      </c>
+      <c r="AB55">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC55">
+        <v>-0.09452491692124203</v>
+      </c>
+      <c r="AD55">
+        <v>0</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
+        <v>-4.21</v>
+      </c>
+      <c r="AH55">
+        <v>0</v>
+      </c>
+      <c r="AI55">
+        <v>0</v>
+      </c>
+      <c r="AJ55">
+        <v>-1.31974921630094</v>
+      </c>
+      <c r="AK55">
+        <v>-0.1740388590326581</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>-0.2</v>
+      </c>
+      <c r="AQ55">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Foresight Environmental Infrastructure Limited (LSE:FGEN)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K56">
+        <v>-21.9</v>
+      </c>
+      <c r="M56">
+        <v>74.53999999999999</v>
+      </c>
+      <c r="N56">
+        <v>0.1258059071729958</v>
+      </c>
+      <c r="O56">
+        <v>-3.40365296803653</v>
+      </c>
+      <c r="P56">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="Q56">
+        <v>0.1140928270042194</v>
+      </c>
+      <c r="R56">
+        <v>-3.08675799086758</v>
+      </c>
+      <c r="S56">
+        <v>6.939999999999998</v>
+      </c>
+      <c r="T56">
+        <v>0.0931043734907432</v>
+      </c>
+      <c r="U56">
+        <v>0.259</v>
+      </c>
+      <c r="V56">
+        <v>0.0004371308016877637</v>
+      </c>
+      <c r="W56">
+        <v>-0.02265673494723774</v>
+      </c>
+      <c r="X56">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y56">
+        <v>-0.09467546885116732</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>-0.02266820272204747</v>
+      </c>
+      <c r="AB56">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC56">
+        <v>-0.09468693662597703</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>-0.259</v>
+      </c>
+      <c r="AH56">
+        <v>0</v>
+      </c>
+      <c r="AI56">
+        <v>0</v>
+      </c>
+      <c r="AJ56">
+        <v>-0.0004373219685904893</v>
+      </c>
+      <c r="AK56">
+        <v>-0.0002684101929548024</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Molten Ventures Plc (LSE:GROW)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>-0.546</v>
+      </c>
+      <c r="G57">
+        <v>-25.85635359116022</v>
+      </c>
+      <c r="H57">
+        <v>-25.85635359116022</v>
+      </c>
+      <c r="I57">
+        <v>-9.779005524861878</v>
+      </c>
+      <c r="J57">
+        <v>-9.779005524861878</v>
+      </c>
+      <c r="K57">
+        <v>-7.91</v>
+      </c>
+      <c r="L57">
+        <v>-2.185082872928177</v>
+      </c>
+      <c r="M57">
+        <v>15.5</v>
+      </c>
+      <c r="N57">
+        <v>0.0212824385555403</v>
+      </c>
+      <c r="O57">
+        <v>-1.959544879898862</v>
+      </c>
+      <c r="P57">
+        <v>-0</v>
+      </c>
+      <c r="Q57">
+        <v>-0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>15.5</v>
+      </c>
+      <c r="T57">
+        <v>1</v>
+      </c>
+      <c r="U57">
+        <v>110.2</v>
+      </c>
+      <c r="V57">
+        <v>0.1513112728271317</v>
+      </c>
+      <c r="W57">
+        <v>-0.0057657263648954</v>
+      </c>
+      <c r="X57">
+        <v>0.07639272287732989</v>
+      </c>
+      <c r="Y57">
+        <v>-0.08215844924222529</v>
+      </c>
+      <c r="Z57">
+        <v>0.002517035182867473</v>
+      </c>
+      <c r="AA57">
+        <v>-0.02461410095953275</v>
+      </c>
+      <c r="AB57">
+        <v>0.07084922946878272</v>
+      </c>
+      <c r="AC57">
+        <v>-0.09546333042831547</v>
+      </c>
+      <c r="AD57">
+        <v>162</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>162</v>
+      </c>
+      <c r="AG57">
+        <v>51.8</v>
+      </c>
+      <c r="AH57">
+        <v>0.1819611366954959</v>
+      </c>
+      <c r="AI57">
+        <v>0.09117514633048177</v>
+      </c>
+      <c r="AJ57">
+        <v>0.0664017433662351</v>
+      </c>
+      <c r="AK57">
+        <v>0.03108124324972999</v>
+      </c>
+      <c r="AL57">
+        <v>16.9</v>
+      </c>
+      <c r="AM57">
+        <v>14.76</v>
+      </c>
+      <c r="AN57">
+        <v>-4.563380281690141</v>
+      </c>
+      <c r="AO57">
+        <v>-2.094674556213018</v>
+      </c>
+      <c r="AP57">
+        <v>-1.459154929577465</v>
+      </c>
+      <c r="AQ57">
+        <v>-2.398373983739837</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kelso Group Holdings Plc (LSE:KLSO)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>-1.095505617977528</v>
+      </c>
+      <c r="J58">
+        <v>-1.095505617977528</v>
+      </c>
+      <c r="K58">
+        <v>-0.187</v>
+      </c>
+      <c r="L58">
+        <v>-1.050561797752809</v>
+      </c>
+      <c r="M58">
+        <v>0.115</v>
+      </c>
+      <c r="N58">
+        <v>0.008914728682170543</v>
+      </c>
+      <c r="O58">
+        <v>-0.6149732620320856</v>
+      </c>
+      <c r="P58">
+        <v>-0</v>
+      </c>
+      <c r="Q58">
+        <v>-0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0.115</v>
+      </c>
+      <c r="T58">
+        <v>1</v>
+      </c>
+      <c r="U58">
+        <v>0.396</v>
+      </c>
+      <c r="V58">
+        <v>0.03069767441860465</v>
+      </c>
+      <c r="W58">
+        <v>-0.02115384615384616</v>
+      </c>
+      <c r="X58">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y58">
+        <v>-0.09317258005777573</v>
+      </c>
+      <c r="Z58">
+        <v>0.03617886178861789</v>
+      </c>
+      <c r="AA58">
+        <v>-0.03963414634146342</v>
+      </c>
+      <c r="AB58">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC58">
+        <v>-0.111652880245393</v>
+      </c>
+      <c r="AD58">
+        <v>0</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>-0.396</v>
+      </c>
+      <c r="AH58">
+        <v>0</v>
+      </c>
+      <c r="AI58">
+        <v>0</v>
+      </c>
+      <c r="AJ58">
+        <v>-0.03166986564299425</v>
+      </c>
+      <c r="AK58">
+        <v>-0.03734439834024897</v>
+      </c>
+      <c r="AL58">
+        <v>0.092</v>
+      </c>
+      <c r="AM58">
+        <v>0.08399999999999999</v>
+      </c>
+      <c r="AO58">
+        <v>-2.119565217391305</v>
+      </c>
+      <c r="AQ58">
+        <v>-2.321428571428572</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Frontier IP Group Plc (AIM:FIPP)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D59">
+        <v>-0.15</v>
+      </c>
+      <c r="G59">
+        <v>-0.9497907949790795</v>
+      </c>
+      <c r="H59">
+        <v>-0.9497907949790795</v>
+      </c>
+      <c r="I59">
+        <v>-0.9088138486152716</v>
+      </c>
+      <c r="J59">
+        <v>-0.9088138486152716</v>
+      </c>
+      <c r="K59">
+        <v>-1.42</v>
+      </c>
+      <c r="L59">
+        <v>-0.5941422594142258</v>
+      </c>
+      <c r="M59">
+        <v>-0</v>
+      </c>
+      <c r="N59">
+        <v>-0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>-0</v>
+      </c>
+      <c r="Q59">
+        <v>-0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>2.9</v>
+      </c>
+      <c r="V59">
+        <v>0.1542553191489362</v>
+      </c>
+      <c r="W59">
+        <v>-0.02452504317789292</v>
+      </c>
+      <c r="X59">
+        <v>0.07214981937063156</v>
+      </c>
+      <c r="Y59">
+        <v>-0.09667486254852448</v>
+      </c>
+      <c r="Z59">
+        <v>0.04811241751068742</v>
+      </c>
+      <c r="AA59">
+        <v>-0.04372523132407262</v>
+      </c>
+      <c r="AB59">
+        <v>0.07197617217229391</v>
+      </c>
+      <c r="AC59">
+        <v>-0.1157014034963665</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
+      <c r="AE59">
+        <v>0.125325490952498</v>
+      </c>
+      <c r="AF59">
+        <v>0.125325490952498</v>
+      </c>
+      <c r="AG59">
+        <v>-2.774674509047502</v>
+      </c>
+      <c r="AH59">
+        <v>0.006622104915046851</v>
+      </c>
+      <c r="AI59">
+        <v>0.002209339300705943</v>
+      </c>
+      <c r="AJ59">
+        <v>-0.1731430984421511</v>
+      </c>
+      <c r="AK59">
+        <v>-0.05154960947730631</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>-0.595</v>
+      </c>
+      <c r="AN59">
+        <v>-0</v>
+      </c>
+      <c r="AP59">
+        <v>1.298397056175715</v>
+      </c>
+      <c r="AQ59">
+        <v>3.831932773109243</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Mindflair Plc (AIM:MFAI)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K60">
+        <v>-0.643</v>
+      </c>
+      <c r="M60">
+        <v>-0</v>
+      </c>
+      <c r="N60">
+        <v>-0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>-0</v>
+      </c>
+      <c r="Q60">
+        <v>-0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0.454</v>
+      </c>
+      <c r="V60">
+        <v>0.1650909090909091</v>
+      </c>
+      <c r="W60">
+        <v>-0.06921420882669538</v>
+      </c>
+      <c r="X60">
+        <v>0.08446071490197615</v>
+      </c>
+      <c r="Y60">
+        <v>-0.1536749237286715</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>-0.05222166749875188</v>
+      </c>
+      <c r="AB60">
+        <v>0.07548624737751479</v>
+      </c>
+      <c r="AC60">
+        <v>-0.1277079148762667</v>
+      </c>
+      <c r="AD60">
+        <v>1.74</v>
+      </c>
+      <c r="AE60">
+        <v>0</v>
+      </c>
+      <c r="AF60">
+        <v>1.74</v>
+      </c>
+      <c r="AG60">
+        <v>1.286</v>
+      </c>
+      <c r="AH60">
+        <v>0.3875278396436526</v>
+      </c>
+      <c r="AI60">
+        <v>0.1553571428571428</v>
+      </c>
+      <c r="AJ60">
+        <v>0.3186323092170466</v>
+      </c>
+      <c r="AK60">
+        <v>0.1196724362553508</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>-0.005</v>
+      </c>
+      <c r="AQ60">
+        <v>104.6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Eight Capital Partners Plc (DB:ECS)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D61">
+        <v>-0.237</v>
+      </c>
+      <c r="G61">
+        <v>-15.43478260869565</v>
+      </c>
+      <c r="H61">
+        <v>-15.43478260869565</v>
+      </c>
+      <c r="I61">
+        <v>-26.08695652173913</v>
+      </c>
+      <c r="J61">
+        <v>-26.08695652173913</v>
+      </c>
+      <c r="K61">
+        <v>-27.3</v>
+      </c>
+      <c r="L61">
+        <v>-296.7391304347826</v>
+      </c>
+      <c r="M61">
+        <v>-0</v>
+      </c>
+      <c r="N61">
+        <v>-0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>-0</v>
+      </c>
+      <c r="Q61">
+        <v>-0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0.053</v>
+      </c>
+      <c r="V61">
+        <v>0.0005463917525773196</v>
+      </c>
+      <c r="W61">
+        <v>-0.8076923076923078</v>
+      </c>
+      <c r="X61">
+        <v>0.0722437555119195</v>
+      </c>
+      <c r="Y61">
+        <v>-0.8799360632042273</v>
+      </c>
+      <c r="Z61">
+        <v>0.002349996168484508</v>
+      </c>
+      <c r="AA61">
+        <v>-0.06130424787350891</v>
+      </c>
+      <c r="AB61">
+        <v>0.07196723084321426</v>
+      </c>
+      <c r="AC61">
+        <v>-0.1332714787167232</v>
+      </c>
+      <c r="AD61">
+        <v>1.11</v>
+      </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>1.11</v>
+      </c>
+      <c r="AG61">
+        <v>1.057</v>
+      </c>
+      <c r="AH61">
+        <v>0.0113138314137193</v>
+      </c>
+      <c r="AI61">
+        <v>0.07110826393337605</v>
+      </c>
+      <c r="AJ61">
+        <v>0.01077944460874797</v>
+      </c>
+      <c r="AK61">
+        <v>0.06794369094298387</v>
+      </c>
+      <c r="AL61">
+        <v>0.13</v>
+      </c>
+      <c r="AM61">
+        <v>-0.794</v>
+      </c>
+      <c r="AN61">
+        <v>-0.4683544303797468</v>
+      </c>
+      <c r="AO61">
+        <v>-18.46153846153846</v>
+      </c>
+      <c r="AP61">
+        <v>-0.4459915611814346</v>
+      </c>
+      <c r="AQ61">
+        <v>3.022670025188916</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tern Plc (AIM:TERN)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>-0.117</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>-27.61904761904762</v>
+      </c>
+      <c r="J62">
+        <v>-27.61904761904762</v>
+      </c>
+      <c r="K62">
+        <v>-15.7</v>
+      </c>
+      <c r="L62">
+        <v>-249.2063492063492</v>
+      </c>
+      <c r="M62">
+        <v>-0</v>
+      </c>
+      <c r="N62">
+        <v>-0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>-0</v>
+      </c>
+      <c r="Q62">
+        <v>-0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0.153</v>
+      </c>
+      <c r="V62">
+        <v>0.01766743648960739</v>
+      </c>
+      <c r="W62">
+        <v>-0.5567375886524822</v>
+      </c>
+      <c r="X62">
+        <v>0.07259775617403658</v>
+      </c>
+      <c r="Y62">
+        <v>-0.6293353448265189</v>
+      </c>
+      <c r="Z62">
+        <v>0.002272809264403478</v>
+      </c>
+      <c r="AA62">
+        <v>-0.06277282730257225</v>
+      </c>
+      <c r="AB62">
+        <v>0.07188852455455597</v>
+      </c>
+      <c r="AC62">
+        <v>-0.1346613518571282</v>
+      </c>
+      <c r="AD62">
+        <v>0.255</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0.255</v>
+      </c>
+      <c r="AG62">
+        <v>0.102</v>
+      </c>
+      <c r="AH62">
+        <v>0.02860347728547392</v>
+      </c>
+      <c r="AI62">
+        <v>0.01853871319520175</v>
+      </c>
+      <c r="AJ62">
+        <v>0.01164117781328464</v>
+      </c>
+      <c r="AK62">
+        <v>0.007498897220996913</v>
+      </c>
+      <c r="AL62">
+        <v>0</v>
+      </c>
+      <c r="AM62">
+        <v>-0.075</v>
+      </c>
+      <c r="AQ62">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tavistock Investments Plc (AIM:TAVI)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D63">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="G63">
+        <v>0.01058027079303675</v>
+      </c>
+      <c r="H63">
+        <v>0.01058027079303675</v>
+      </c>
+      <c r="I63">
+        <v>-0.03926499032882011</v>
+      </c>
+      <c r="J63">
+        <v>-0.03926499032882011</v>
+      </c>
+      <c r="K63">
+        <v>-3.35</v>
+      </c>
+      <c r="L63">
+        <v>-0.06479690522243714</v>
+      </c>
+      <c r="M63">
+        <v>0.525</v>
+      </c>
+      <c r="N63">
+        <v>0.01761744966442953</v>
+      </c>
+      <c r="O63">
+        <v>-0.1567164179104478</v>
+      </c>
+      <c r="P63">
+        <v>0.525</v>
+      </c>
+      <c r="Q63">
+        <v>0.01761744966442953</v>
+      </c>
+      <c r="R63">
+        <v>-0.1567164179104478</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>3.9</v>
+      </c>
+      <c r="V63">
+        <v>0.1308724832214765</v>
+      </c>
+      <c r="W63">
+        <v>-0.06740442655935613</v>
+      </c>
+      <c r="X63">
+        <v>0.07395214557352305</v>
+      </c>
+      <c r="Y63">
+        <v>-0.1413565721328792</v>
+      </c>
+      <c r="Z63">
+        <v>1.70796167822927</v>
+      </c>
+      <c r="AA63">
+        <v>-0.06706309877766764</v>
+      </c>
+      <c r="AB63">
+        <v>0.07161121763540805</v>
+      </c>
+      <c r="AC63">
+        <v>-0.1386743164130757</v>
+      </c>
+      <c r="AD63">
+        <v>2.93</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>2.93</v>
+      </c>
+      <c r="AG63">
+        <v>-0.9699999999999998</v>
+      </c>
+      <c r="AH63">
+        <v>0.0895203177512985</v>
+      </c>
+      <c r="AI63">
+        <v>0.05238691221169319</v>
+      </c>
+      <c r="AJ63">
+        <v>-0.03364550815123134</v>
+      </c>
+      <c r="AK63">
+        <v>-0.01864309052469728</v>
+      </c>
+      <c r="AL63">
+        <v>0.028</v>
+      </c>
+      <c r="AM63">
+        <v>-0.286</v>
+      </c>
+      <c r="AN63">
+        <v>-3.975576662143827</v>
+      </c>
+      <c r="AO63">
+        <v>-72.49999999999999</v>
+      </c>
+      <c r="AP63">
+        <v>1.316146540027137</v>
+      </c>
+      <c r="AQ63">
+        <v>7.097902097902097</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LMS Capital plc (LSE:LMS)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K64">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="M64">
+        <v>0.944</v>
+      </c>
+      <c r="N64">
+        <v>0.05552941176470588</v>
+      </c>
+      <c r="O64">
+        <v>-0.1005324813631523</v>
+      </c>
+      <c r="P64">
+        <v>0.944</v>
+      </c>
+      <c r="Q64">
+        <v>0.05552941176470588</v>
+      </c>
+      <c r="R64">
+        <v>-0.1005324813631523</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>15.9</v>
+      </c>
+      <c r="V64">
+        <v>0.9352941176470588</v>
+      </c>
+      <c r="W64">
+        <v>-0.1656084656084656</v>
+      </c>
+      <c r="X64">
+        <v>0.08439551858504929</v>
+      </c>
+      <c r="Y64">
+        <v>-0.2500039841935149</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>-0.1017334777898158</v>
+      </c>
+      <c r="AB64">
+        <v>0.07026029475316513</v>
+      </c>
+      <c r="AC64">
+        <v>-0.1719937725429809</v>
+      </c>
+      <c r="AD64">
+        <v>10.7</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>10.7</v>
+      </c>
+      <c r="AG64">
+        <v>-5.200000000000001</v>
+      </c>
+      <c r="AH64">
+        <v>0.3862815884476534</v>
+      </c>
+      <c r="AI64">
+        <v>0.1883802816901408</v>
+      </c>
+      <c r="AJ64">
+        <v>-0.440677966101695</v>
+      </c>
+      <c r="AK64">
+        <v>-0.1271393643031785</v>
+      </c>
+      <c r="AL64">
+        <v>0</v>
+      </c>
+      <c r="AM64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Harmony Energy Income Trust Plc (LSE:HEIT)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K65">
+        <v>-36.4</v>
+      </c>
+      <c r="M65">
+        <v>17.1</v>
+      </c>
+      <c r="N65">
+        <v>0.09238249594813615</v>
+      </c>
+      <c r="O65">
+        <v>-0.4697802197802198</v>
+      </c>
+      <c r="P65">
+        <v>17.1</v>
+      </c>
+      <c r="Q65">
+        <v>0.09238249594813615</v>
+      </c>
+      <c r="R65">
+        <v>-0.4697802197802198</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>14.9</v>
+      </c>
+      <c r="V65">
+        <v>0.08049702863317126</v>
+      </c>
+      <c r="W65">
+        <v>-0.1088842357164224</v>
+      </c>
+      <c r="X65">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y65">
+        <v>-0.1809029696203519</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>-0.1114888664277619</v>
+      </c>
+      <c r="AB65">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC65">
+        <v>-0.1835076003316915</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>-14.9</v>
+      </c>
+      <c r="AH65">
+        <v>0</v>
+      </c>
+      <c r="AI65">
+        <v>0</v>
+      </c>
+      <c r="AJ65">
+        <v>-0.08754406580493537</v>
+      </c>
+      <c r="AK65">
+        <v>-0.05757341576506955</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AssetCo plc (AIM:ASTO)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D66">
+        <v>-0.027</v>
+      </c>
+      <c r="G66">
+        <v>-0.6203208556149733</v>
+      </c>
+      <c r="H66">
+        <v>-0.6203208556149733</v>
+      </c>
+      <c r="I66">
+        <v>-0.3989304812834225</v>
+      </c>
+      <c r="J66">
+        <v>-0.3989304812834225</v>
+      </c>
+      <c r="K66">
+        <v>-19.2</v>
+      </c>
+      <c r="L66">
+        <v>-1.026737967914439</v>
+      </c>
+      <c r="M66">
+        <v>-0</v>
+      </c>
+      <c r="N66">
+        <v>-0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>-0</v>
+      </c>
+      <c r="Q66">
+        <v>-0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>14.2</v>
+      </c>
+      <c r="V66">
+        <v>0.262962962962963</v>
+      </c>
+      <c r="W66">
+        <v>-0.2296650717703349</v>
+      </c>
+      <c r="X66">
+        <v>0.07257588199938808</v>
+      </c>
+      <c r="Y66">
+        <v>-0.302240953769723</v>
+      </c>
+      <c r="Z66">
+        <v>0.3594080338266385</v>
+      </c>
+      <c r="AA66">
+        <v>-0.1433788199115895</v>
+      </c>
+      <c r="AB66">
+        <v>0.07184164677808778</v>
+      </c>
+      <c r="AC66">
+        <v>-0.2152204666896773</v>
+      </c>
+      <c r="AD66">
+        <v>1.53</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>1.53</v>
+      </c>
+      <c r="AG66">
+        <v>-12.67</v>
+      </c>
+      <c r="AH66">
+        <v>0.02755267423014587</v>
+      </c>
+      <c r="AI66">
+        <v>0.02262309625905663</v>
+      </c>
+      <c r="AJ66">
+        <v>-0.3065569804016453</v>
+      </c>
+      <c r="AK66">
+        <v>-0.2371326969867116</v>
+      </c>
+      <c r="AL66">
+        <v>0.289</v>
+      </c>
+      <c r="AM66">
+        <v>-2.821</v>
+      </c>
+      <c r="AN66">
+        <v>-0.2151898734177215</v>
+      </c>
+      <c r="AO66">
+        <v>-25.81314878892734</v>
+      </c>
+      <c r="AP66">
+        <v>1.781997187060478</v>
+      </c>
+      <c r="AQ66">
+        <v>2.644452321871677</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Triple Point Energy Transition plc (LSE:TENT)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K67">
+        <v>-16.6</v>
+      </c>
+      <c r="M67">
+        <v>7.37</v>
+      </c>
+      <c r="N67">
+        <v>0.1304424778761062</v>
+      </c>
+      <c r="O67">
+        <v>-0.4439759036144578</v>
+      </c>
+      <c r="P67">
+        <v>7.37</v>
+      </c>
+      <c r="Q67">
+        <v>0.1304424778761062</v>
+      </c>
+      <c r="R67">
+        <v>-0.4439759036144578</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>5.58</v>
+      </c>
+      <c r="V67">
+        <v>0.09876106194690265</v>
+      </c>
+      <c r="W67">
+        <v>-0.1429801894918174</v>
+      </c>
+      <c r="X67">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y67">
+        <v>-0.214998923395747</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>-0.1466172054407349</v>
+      </c>
+      <c r="AB67">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC67">
+        <v>-0.2186359393446644</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>-5.58</v>
+      </c>
+      <c r="AH67">
+        <v>0</v>
+      </c>
+      <c r="AI67">
+        <v>0</v>
+      </c>
+      <c r="AJ67">
+        <v>-0.1095836606441477</v>
+      </c>
+      <c r="AK67">
+        <v>-0.05698529411764706</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>IP Group Plc (LSE:IPO)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K68">
+        <v>-286</v>
+      </c>
+      <c r="M68">
+        <v>17.1</v>
+      </c>
+      <c r="N68">
+        <v>0.02586598094085615</v>
+      </c>
+      <c r="O68">
+        <v>-0.0597902097902098</v>
+      </c>
+      <c r="P68">
+        <v>6.7</v>
+      </c>
+      <c r="Q68">
+        <v>0.0101346241113296</v>
+      </c>
+      <c r="R68">
+        <v>-0.02342657342657343</v>
+      </c>
+      <c r="S68">
+        <v>10.4</v>
+      </c>
+      <c r="T68">
+        <v>0.6081871345029241</v>
+      </c>
+      <c r="U68">
+        <v>115.4</v>
+      </c>
+      <c r="V68">
+        <v>0.1745575555891696</v>
+      </c>
+      <c r="W68">
+        <v>-0.1704206888332737</v>
+      </c>
+      <c r="X68">
+        <v>0.07773264116033354</v>
+      </c>
+      <c r="Y68">
+        <v>-0.2481533299936073</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>-0.1696662853687647</v>
+      </c>
+      <c r="AB68">
+        <v>0.07057162988367452</v>
+      </c>
+      <c r="AC68">
+        <v>-0.2402379152524392</v>
+      </c>
+      <c r="AD68">
+        <v>192.1</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>192.1</v>
+      </c>
+      <c r="AG68">
+        <v>76.69999999999999</v>
+      </c>
+      <c r="AH68">
+        <v>0.2251523675574308</v>
+      </c>
+      <c r="AI68">
+        <v>0.1241677978152673</v>
+      </c>
+      <c r="AJ68">
+        <v>0.1039577121171049</v>
+      </c>
+      <c r="AK68">
+        <v>0.05357267583991059</v>
+      </c>
+      <c r="AL68">
+        <v>8.59</v>
+      </c>
+      <c r="AM68">
+        <v>-5.01</v>
+      </c>
+      <c r="AN68">
+        <v>-0.6403333333333333</v>
+      </c>
+      <c r="AO68">
+        <v>-35.0174621653085</v>
+      </c>
+      <c r="AP68">
+        <v>-0.2556666666666667</v>
+      </c>
+      <c r="AQ68">
+        <v>60.03992015968064</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Alpha Growth plc (LSE:ALGW)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G69">
+        <v>-0.2769010043041607</v>
+      </c>
+      <c r="H69">
+        <v>-0.2769010043041607</v>
+      </c>
+      <c r="I69">
+        <v>-0.2352941176470588</v>
+      </c>
+      <c r="J69">
+        <v>-0.2352941176470588</v>
+      </c>
+      <c r="K69">
+        <v>-1.37</v>
+      </c>
+      <c r="L69">
+        <v>-0.1965566714490675</v>
+      </c>
+      <c r="M69">
+        <v>-0</v>
+      </c>
+      <c r="N69">
+        <v>-0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>-0</v>
+      </c>
+      <c r="Q69">
+        <v>-0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>8.68</v>
+      </c>
+      <c r="V69">
+        <v>0.8985507246376812</v>
+      </c>
+      <c r="W69">
+        <v>-0.1604215456674473</v>
+      </c>
+      <c r="X69">
+        <v>0.09949954971938371</v>
+      </c>
+      <c r="Y69">
+        <v>-0.2599210953868311</v>
+      </c>
+      <c r="Z69">
+        <v>0.8054079038594871</v>
+      </c>
+      <c r="AA69">
+        <v>-0.1895077420845852</v>
+      </c>
+      <c r="AB69">
+        <v>0.06936523721923163</v>
+      </c>
+      <c r="AC69">
+        <v>-0.2588729793038168</v>
+      </c>
+      <c r="AD69">
+        <v>13.5</v>
+      </c>
+      <c r="AE69">
+        <v>0</v>
+      </c>
+      <c r="AF69">
+        <v>13.5</v>
+      </c>
+      <c r="AG69">
+        <v>4.82</v>
+      </c>
+      <c r="AH69">
+        <v>0.582901554404145</v>
+      </c>
+      <c r="AI69">
+        <v>0.6556580864497329</v>
+      </c>
+      <c r="AJ69">
+        <v>0.3328729281767956</v>
+      </c>
+      <c r="AK69">
+        <v>0.4047019311502939</v>
+      </c>
+      <c r="AL69">
+        <v>0.013</v>
+      </c>
+      <c r="AM69">
+        <v>0.013</v>
+      </c>
+      <c r="AN69">
+        <v>-8.544303797468354</v>
+      </c>
+      <c r="AO69">
+        <v>-126.1538461538461</v>
+      </c>
+      <c r="AP69">
+        <v>-3.050632911392405</v>
+      </c>
+      <c r="AQ69">
+        <v>-126.1538461538461</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Intuitive Investments Group Plc (LSE:IIG)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K70">
+        <v>-3.06</v>
+      </c>
+      <c r="M70">
+        <v>-0</v>
+      </c>
+      <c r="N70">
+        <v>-0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>-0</v>
+      </c>
+      <c r="Q70">
+        <v>-0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>1.42</v>
+      </c>
+      <c r="V70">
+        <v>0.004367886804060288</v>
+      </c>
+      <c r="W70">
+        <v>-0.2390625</v>
+      </c>
+      <c r="X70">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y70">
+        <v>-0.3110812339039296</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>-0.1882022471910112</v>
+      </c>
+      <c r="AB70">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC70">
+        <v>-0.2602209810949408</v>
+      </c>
+      <c r="AD70">
+        <v>0</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>0</v>
+      </c>
+      <c r="AG70">
+        <v>-1.42</v>
+      </c>
+      <c r="AH70">
+        <v>0</v>
+      </c>
+      <c r="AI70">
+        <v>0</v>
+      </c>
+      <c r="AJ70">
+        <v>-0.004387048937221947</v>
+      </c>
+      <c r="AK70">
+        <v>-0.003414446474944695</v>
+      </c>
+      <c r="AL70">
+        <v>0</v>
+      </c>
+      <c r="AM70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Vela Technologies PLC (AIM:VELA)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K71">
+        <v>-5.38</v>
+      </c>
+      <c r="M71">
+        <v>-0</v>
+      </c>
+      <c r="N71">
+        <v>-0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>-0</v>
+      </c>
+      <c r="Q71">
+        <v>-0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0.138</v>
+      </c>
+      <c r="V71">
+        <v>0.09718309859154931</v>
+      </c>
+      <c r="W71">
+        <v>-0.5873362445414847</v>
+      </c>
+      <c r="X71">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y71">
+        <v>-0.6593549784454142</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+      <c r="AA71">
+        <v>-0.2324051743038807</v>
+      </c>
+      <c r="AB71">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC71">
+        <v>-0.3044239082078103</v>
+      </c>
+      <c r="AD71">
+        <v>0</v>
+      </c>
+      <c r="AE71">
+        <v>0</v>
+      </c>
+      <c r="AF71">
+        <v>0</v>
+      </c>
+      <c r="AG71">
+        <v>-0.138</v>
+      </c>
+      <c r="AH71">
+        <v>0</v>
+      </c>
+      <c r="AI71">
+        <v>0</v>
+      </c>
+      <c r="AJ71">
+        <v>-0.1076443057722309</v>
+      </c>
+      <c r="AK71">
+        <v>-0.02781136638452237</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>-0.031</v>
+      </c>
+      <c r="AQ71">
+        <v>68.38709677419355</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Kazera Global plc (AIM:KZG)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G72">
+        <v>-300</v>
+      </c>
+      <c r="H72">
+        <v>-300</v>
+      </c>
+      <c r="I72">
+        <v>-525</v>
+      </c>
+      <c r="J72">
+        <v>-525</v>
+      </c>
+      <c r="K72">
+        <v>-3.57</v>
+      </c>
+      <c r="L72">
+        <v>-446.2499999999999</v>
+      </c>
+      <c r="M72">
+        <v>-0</v>
+      </c>
+      <c r="N72">
+        <v>-0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>-0</v>
+      </c>
+      <c r="Q72">
+        <v>-0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0.077</v>
+      </c>
+      <c r="V72">
+        <v>0.003649289099526066</v>
+      </c>
+      <c r="W72">
+        <v>-0.2975</v>
+      </c>
+      <c r="X72">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y72">
+        <v>-0.3695187339039295</v>
+      </c>
+      <c r="Z72">
+        <v>0.000716524854455889</v>
+      </c>
+      <c r="AA72">
+        <v>-0.3761755485893417</v>
+      </c>
+      <c r="AB72">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC72">
+        <v>-0.4481942824932713</v>
+      </c>
+      <c r="AD72">
+        <v>0</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>0</v>
+      </c>
+      <c r="AG72">
+        <v>-0.077</v>
+      </c>
+      <c r="AH72">
+        <v>0</v>
+      </c>
+      <c r="AI72">
+        <v>0</v>
+      </c>
+      <c r="AJ72">
+        <v>-0.00366265518717595</v>
+      </c>
+      <c r="AK72">
+        <v>-0.007759750075581981</v>
+      </c>
+      <c r="AL72">
+        <v>0</v>
+      </c>
+      <c r="AM72">
+        <v>0</v>
+      </c>
+      <c r="AN72">
+        <v>-0</v>
+      </c>
+      <c r="AP72">
+        <v>0.03208333333333333</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Gunsynd Plc (AIM:GUN)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K73">
+        <v>-1.09</v>
+      </c>
+      <c r="M73">
+        <v>-0</v>
+      </c>
+      <c r="N73">
+        <v>-0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>-0</v>
+      </c>
+      <c r="Q73">
+        <v>-0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>0.19</v>
+      </c>
+      <c r="V73">
+        <v>0.1484375</v>
+      </c>
+      <c r="W73">
+        <v>-0.3949275362318841</v>
+      </c>
+      <c r="X73">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y73">
+        <v>-0.4669462701358137</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73">
+        <v>-0.3919183993723029</v>
+      </c>
+      <c r="AB73">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC73">
+        <v>-0.4639371332762324</v>
+      </c>
+      <c r="AD73">
+        <v>0</v>
+      </c>
+      <c r="AE73">
+        <v>0</v>
+      </c>
+      <c r="AF73">
+        <v>0</v>
+      </c>
+      <c r="AG73">
+        <v>-0.19</v>
+      </c>
+      <c r="AH73">
+        <v>0</v>
+      </c>
+      <c r="AI73">
+        <v>0</v>
+      </c>
+      <c r="AJ73">
+        <v>-0.1743119266055046</v>
+      </c>
+      <c r="AK73">
+        <v>-0.1049723756906077</v>
+      </c>
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>-0.004</v>
+      </c>
+      <c r="AQ73">
+        <v>249.75</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Blue Star Capital plc (AIM:BLU)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K74">
+        <v>-6.76</v>
+      </c>
+      <c r="M74">
+        <v>-0</v>
+      </c>
+      <c r="N74">
+        <v>-0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>-0</v>
+      </c>
+      <c r="Q74">
+        <v>-0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>0.051</v>
+      </c>
+      <c r="V74">
+        <v>0.04722222222222221</v>
+      </c>
+      <c r="W74">
+        <v>-0.52</v>
+      </c>
+      <c r="X74">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y74">
+        <v>-0.5920187339039296</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+      <c r="AA74">
+        <v>-0.527836339501835</v>
+      </c>
+      <c r="AB74">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC74">
+        <v>-0.5998550734057645</v>
+      </c>
+      <c r="AD74">
+        <v>0</v>
+      </c>
+      <c r="AE74">
+        <v>0</v>
+      </c>
+      <c r="AF74">
+        <v>0</v>
+      </c>
+      <c r="AG74">
+        <v>-0.051</v>
+      </c>
+      <c r="AH74">
+        <v>0</v>
+      </c>
+      <c r="AI74">
+        <v>0</v>
+      </c>
+      <c r="AJ74">
+        <v>-0.04956268221574343</v>
+      </c>
+      <c r="AK74">
+        <v>-0.007763738773024813</v>
+      </c>
+      <c r="AL74">
+        <v>0</v>
+      </c>
+      <c r="AM74">
+        <v>-0.001</v>
+      </c>
+      <c r="AQ74">
+        <v>6760</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Argo Group Limited (AIM:ARGO)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D75">
+        <v>0.0519</v>
+      </c>
+      <c r="G75">
+        <v>-2.382495948136143</v>
+      </c>
+      <c r="H75">
+        <v>-2.382495948136143</v>
+      </c>
+      <c r="I75">
+        <v>-1.880064829821718</v>
+      </c>
+      <c r="J75">
+        <v>-1.880064829821718</v>
+      </c>
+      <c r="K75">
+        <v>-12.4</v>
+      </c>
+      <c r="L75">
+        <v>-2.009724473257699</v>
+      </c>
+      <c r="M75">
+        <v>-0</v>
+      </c>
+      <c r="N75">
+        <v>-0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>-0</v>
+      </c>
+      <c r="Q75">
+        <v>-0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>5.09</v>
+      </c>
+      <c r="V75">
+        <v>2.61025641025641</v>
+      </c>
+      <c r="W75">
+        <v>-0.6294416243654822</v>
+      </c>
+      <c r="X75">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y75">
+        <v>-0.7014603582694118</v>
+      </c>
+      <c r="Z75">
+        <v>0.3342361863488624</v>
+      </c>
+      <c r="AA75">
+        <v>-0.6283856988082339</v>
+      </c>
+      <c r="AB75">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC75">
+        <v>-0.7004044327121635</v>
+      </c>
+      <c r="AD75">
+        <v>0</v>
+      </c>
+      <c r="AE75">
+        <v>0</v>
+      </c>
+      <c r="AF75">
+        <v>0</v>
+      </c>
+      <c r="AG75">
+        <v>-5.09</v>
+      </c>
+      <c r="AH75">
+        <v>0</v>
+      </c>
+      <c r="AI75">
+        <v>0</v>
+      </c>
+      <c r="AJ75">
+        <v>1.621019108280255</v>
+      </c>
+      <c r="AK75">
+        <v>-2.345622119815668</v>
+      </c>
+      <c r="AL75">
+        <v>0.482</v>
+      </c>
+      <c r="AM75">
+        <v>0.482</v>
+      </c>
+      <c r="AN75">
+        <v>-0</v>
+      </c>
+      <c r="AO75">
+        <v>-24.06639004149378</v>
+      </c>
+      <c r="AP75">
+        <v>0.4387931034482759</v>
+      </c>
+      <c r="AQ75">
+        <v>-24.06639004149378</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Braveheart Investment Group plc (AIM:BRH)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K76">
+        <v>-8.68</v>
+      </c>
+      <c r="M76">
+        <v>-0</v>
+      </c>
+      <c r="N76">
+        <v>-0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>-0</v>
+      </c>
+      <c r="Q76">
+        <v>-0</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>1.47</v>
+      </c>
+      <c r="V76">
+        <v>0.3878627968337731</v>
+      </c>
+      <c r="W76">
+        <v>-0.7233333333333333</v>
+      </c>
+      <c r="X76">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y76">
+        <v>-0.7953520672372628</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+      <c r="AA76">
+        <v>-0.8442630070355251</v>
+      </c>
+      <c r="AB76">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC76">
+        <v>-0.9162817409394547</v>
+      </c>
+      <c r="AD76">
+        <v>0</v>
+      </c>
+      <c r="AE76">
+        <v>0</v>
+      </c>
+      <c r="AF76">
+        <v>0</v>
+      </c>
+      <c r="AG76">
+        <v>-1.47</v>
+      </c>
+      <c r="AH76">
+        <v>0</v>
+      </c>
+      <c r="AI76">
+        <v>0</v>
+      </c>
+      <c r="AJ76">
+        <v>-0.6336206896551724</v>
+      </c>
+      <c r="AK76">
+        <v>-0.4651898734177215</v>
+      </c>
+      <c r="AL76">
+        <v>0</v>
+      </c>
+      <c r="AM76">
+        <v>-0.054</v>
+      </c>
+      <c r="AN76">
+        <v>-0</v>
+      </c>
+      <c r="AP76">
+        <v>0.1512345679012345</v>
+      </c>
+      <c r="AQ76">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Quantum Blockchain Technologies Plc (AIM:QBT)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K77">
+        <v>-4.4</v>
+      </c>
+      <c r="M77">
+        <v>-0</v>
+      </c>
+      <c r="N77">
+        <v>-0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>-0</v>
+      </c>
+      <c r="Q77">
+        <v>-0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>1.7</v>
+      </c>
+      <c r="V77">
+        <v>0.1619047619047619</v>
+      </c>
+      <c r="W77">
+        <v>1.290322580645161</v>
+      </c>
+      <c r="X77">
+        <v>0.08621430554620002</v>
+      </c>
+      <c r="Y77">
+        <v>1.204108275098961</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>-0.8777754720896451</v>
+      </c>
+      <c r="AB77">
+        <v>0.07011022532973488</v>
+      </c>
+      <c r="AC77">
+        <v>-0.94788569741938</v>
+      </c>
+      <c r="AD77">
+        <v>7.58</v>
+      </c>
+      <c r="AE77">
+        <v>0</v>
+      </c>
+      <c r="AF77">
+        <v>7.58</v>
+      </c>
+      <c r="AG77">
+        <v>5.88</v>
+      </c>
+      <c r="AH77">
+        <v>0.4192477876106195</v>
+      </c>
+      <c r="AI77">
+        <v>1.973958333333333</v>
+      </c>
+      <c r="AJ77">
+        <v>0.358974358974359</v>
+      </c>
+      <c r="AK77">
+        <v>2.74766355140187</v>
+      </c>
+      <c r="AL77">
+        <v>0.278</v>
+      </c>
+      <c r="AM77">
+        <v>0.265</v>
+      </c>
+      <c r="AN77">
+        <v>-1.817745803357314</v>
+      </c>
+      <c r="AO77">
+        <v>-15.2158273381295</v>
+      </c>
+      <c r="AP77">
+        <v>-1.410071942446043</v>
+      </c>
+      <c r="AQ77">
+        <v>-15.9622641509434</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PensionBee Group plc (LSE:PBEE)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G78">
+        <v>-0.3743016759776537</v>
+      </c>
+      <c r="H78">
+        <v>-0.3743016759776537</v>
+      </c>
+      <c r="I78">
+        <v>-0.1793296089385475</v>
+      </c>
+      <c r="J78">
+        <v>-0.1793296089385475</v>
+      </c>
+      <c r="K78">
+        <v>-6.54</v>
+      </c>
+      <c r="L78">
+        <v>-0.1826815642458101</v>
+      </c>
+      <c r="M78">
+        <v>-0</v>
+      </c>
+      <c r="N78">
+        <v>-0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>-0</v>
+      </c>
+      <c r="Q78">
+        <v>-0</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="U78">
+        <v>13.8</v>
+      </c>
+      <c r="V78">
+        <v>0.0290955091714105</v>
+      </c>
+      <c r="W78">
+        <v>-0.3303030303030303</v>
+      </c>
+      <c r="X78">
+        <v>0.07203527608423899</v>
+      </c>
+      <c r="Y78">
+        <v>-0.4023383063872693</v>
+      </c>
+      <c r="Z78">
+        <v>14.88565488565488</v>
+      </c>
+      <c r="AA78">
+        <v>-1</v>
+      </c>
+      <c r="AB78">
+        <v>0.07201333161496193</v>
+      </c>
+      <c r="AC78">
+        <v>-1.072013331614962</v>
+      </c>
+      <c r="AD78">
+        <v>0.399</v>
+      </c>
+      <c r="AE78">
+        <v>0</v>
+      </c>
+      <c r="AF78">
+        <v>0.399</v>
+      </c>
+      <c r="AG78">
+        <v>-13.401</v>
+      </c>
+      <c r="AH78">
+        <v>0.0008405326322574937</v>
+      </c>
+      <c r="AI78">
+        <v>0.02389364632612731</v>
+      </c>
+      <c r="AJ78">
+        <v>-0.02907578449942395</v>
+      </c>
+      <c r="AK78">
+        <v>-4.622628492583648</v>
+      </c>
+      <c r="AL78">
+        <v>0.039</v>
+      </c>
+      <c r="AM78">
+        <v>0.016</v>
+      </c>
+      <c r="AN78">
+        <v>-0.06394230769230769</v>
+      </c>
+      <c r="AO78">
+        <v>-164.6153846153846</v>
+      </c>
+      <c r="AP78">
+        <v>2.147596153846154</v>
+      </c>
+      <c r="AQ78">
+        <v>-401.25</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ajax Resources Plc (LSE:AJAX)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K79">
+        <v>-0.218</v>
+      </c>
+      <c r="M79">
+        <v>-0</v>
+      </c>
+      <c r="N79">
+        <v>-0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>-0</v>
+      </c>
+      <c r="Q79">
+        <v>-0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="U79">
+        <v>0.599</v>
+      </c>
+      <c r="V79">
+        <v>0.3403409090909091</v>
+      </c>
+      <c r="W79">
+        <v>-0.1772357723577236</v>
+      </c>
+      <c r="X79">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y79">
+        <v>-0.2492545062616532</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+      <c r="AA79">
+        <v>-1</v>
+      </c>
+      <c r="AB79">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC79">
+        <v>-1.07201873390393</v>
+      </c>
+      <c r="AD79">
+        <v>0</v>
+      </c>
+      <c r="AE79">
+        <v>0</v>
+      </c>
+      <c r="AF79">
+        <v>0</v>
+      </c>
+      <c r="AG79">
+        <v>-0.599</v>
+      </c>
+      <c r="AH79">
+        <v>0</v>
+      </c>
+      <c r="AI79">
+        <v>0</v>
+      </c>
+      <c r="AJ79">
+        <v>-0.5159345391903531</v>
+      </c>
+      <c r="AK79">
+        <v>-1.328159645232816</v>
+      </c>
+      <c r="AL79">
+        <v>0</v>
+      </c>
+      <c r="AM79">
+        <v>-0.2</v>
+      </c>
+      <c r="AQ79">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tiger Royalties and investments Plc (AIM:TIR)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>-18.375</v>
+      </c>
+      <c r="J80">
+        <v>-18.375</v>
+      </c>
+      <c r="K80">
+        <v>-0.345</v>
+      </c>
+      <c r="L80">
+        <v>-21.5625</v>
+      </c>
+      <c r="M80">
+        <v>-0</v>
+      </c>
+      <c r="N80">
+        <v>-0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>-0</v>
+      </c>
+      <c r="Q80">
+        <v>-0</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="U80">
+        <v>0.064</v>
+      </c>
+      <c r="V80">
+        <v>0.05470085470085471</v>
+      </c>
+      <c r="W80">
+        <v>-1.095238095238095</v>
+      </c>
+      <c r="X80">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y80">
+        <v>-1.167256829142025</v>
+      </c>
+      <c r="Z80">
+        <v>0.07079646017699115</v>
+      </c>
+      <c r="AA80">
+        <v>-1</v>
+      </c>
+      <c r="AB80">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC80">
+        <v>-1.07201873390393</v>
+      </c>
+      <c r="AD80">
+        <v>0</v>
+      </c>
+      <c r="AE80">
+        <v>0</v>
+      </c>
+      <c r="AF80">
+        <v>0</v>
+      </c>
+      <c r="AG80">
+        <v>-0.064</v>
+      </c>
+      <c r="AH80">
+        <v>0</v>
+      </c>
+      <c r="AI80">
+        <v>-0</v>
+      </c>
+      <c r="AJ80">
+        <v>-0.05786618444846293</v>
+      </c>
+      <c r="AK80">
+        <v>0.6808510638297872</v>
+      </c>
+      <c r="AL80">
+        <v>0.032</v>
+      </c>
+      <c r="AM80">
+        <v>0.032</v>
+      </c>
+      <c r="AO80">
+        <v>-9.1875</v>
+      </c>
+      <c r="AQ80">
+        <v>-9.1875</v>
       </c>
     </row>
   </sheetData>
